--- a/financial_models/opportunities/Not Monitored/601166.SS_Valuation_v2.2.xlsx
+++ b/financial_models/opportunities/Not Monitored/601166.SS_Valuation_v2.2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\Not Monitored\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8BF774B-0EE7-4FB0-905C-0622DE2CAB52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25917F1B-7418-4E8B-A6BD-9695D7BCE486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -23,17 +23,16 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost" localSheetId="5">DDM!$C$5</definedName>
-    <definedName name="Equity_Cost">DCF!$C$5</definedName>
+    <definedName name="Equity_Cost">Thesis!$C$80</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth" localSheetId="5">DDM!$F$4</definedName>
-    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
+    <definedName name="Terminal_Growth">Thesis!$C$86</definedName>
+    <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="459">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1378,10 +1377,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CAGR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Market Price</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2439,6 +2434,33 @@
   </si>
   <si>
     <t>DDM</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>DDM Terminal Value</t>
   </si>
 </sst>
 </file>
@@ -3112,7 +3134,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="361">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3837,29 +3859,32 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3939,8 +3964,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF0000"/>
       <color rgb="FF0000FF"/>
-      <color rgb="FFFF0000"/>
       <color rgb="FF003871"/>
       <color rgb="FF005078"/>
       <color rgb="FF002850"/>
@@ -4182,10 +4207,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="325" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F1" s="281" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4204,7 +4229,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4213,10 +4238,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C5" s="327" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4230,7 +4255,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C7" s="277">
         <v>6</v>
@@ -4253,17 +4278,17 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D11" s="49"/>
       <c r="E11" s="34"/>
@@ -4280,17 +4305,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4304,7 +4329,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4331,67 +4356,72 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="348" t="s">
-        <v>365</v>
-      </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="B18" s="351" t="s">
+        <v>364</v>
+      </c>
+      <c r="C18" s="351"/>
+      <c r="D18" s="351"/>
+      <c r="E18" s="351"/>
+      <c r="F18" s="351"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
-        <v xml:space="preserve">Negative Growth </v>
-      </c>
-      <c r="E21" s="5"/>
+        <v xml:space="preserve">Low Growth </v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E21" s="343" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="E22" s="343" t="s">
-        <v>450</v>
+        <v>458</v>
+      </c>
+      <c r="E22" s="348">
+        <v>0.02</v>
       </c>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C23" s="291" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C24" s="291" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4409,14 +4439,14 @@
       </c>
       <c r="C26" s="339">
         <f>C127</f>
-        <v>-125.39563243722989</v>
+        <v>21.752920556327282</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="E26" s="336" t="e">
+        <v>404</v>
+      </c>
+      <c r="E26" s="336">
         <f ca="1">Scenarios!C87</f>
-        <v>#NUM!</v>
+        <v>3.3241061492891966E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4425,7 +4455,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C28" s="344" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4436,7 +4466,7 @@
         <v/>
       </c>
       <c r="E28" s="340" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F28" s="338">
         <v>3</v>
@@ -4444,18 +4474,18 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C29" s="345">
         <f>C144</f>
-        <v>-44.013860217649388</v>
+        <v>9.6117057421017815</v>
       </c>
       <c r="D29" s="345" t="str">
         <f>D144</f>
         <v/>
       </c>
       <c r="E29" s="341" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F29" s="337">
         <v>0.4</v>
@@ -4463,18 +4493,18 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C30" s="346">
         <f>C152</f>
-        <v>-66.891462521769384</v>
+        <v>14.144259076931155</v>
       </c>
       <c r="D30" s="346" t="str">
         <f>D152</f>
         <v/>
       </c>
       <c r="E30" s="342" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F30" s="347">
         <v>0.22</v>
@@ -4482,18 +4512,18 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C31" s="346">
         <f>C160</f>
-        <v>-96.811373105304924</v>
+        <v>19.999892480445755</v>
       </c>
       <c r="D31" s="346" t="str">
         <f>D160</f>
         <v/>
       </c>
       <c r="E31" s="342" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F31" s="347">
         <v>0.08</v>
@@ -4501,18 +4531,18 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C32" s="346">
         <f>C168</f>
-        <v>-86.708193186576011</v>
+        <v>18.029240328562945</v>
       </c>
       <c r="D32" s="346" t="str">
         <f>D168</f>
         <v/>
       </c>
       <c r="E32" s="342" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F32" s="347">
         <v>0.12</v>
@@ -4524,7 +4554,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="247" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4533,22 +4563,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="348" t="s">
-        <v>366</v>
-      </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="B36" s="351" t="s">
+        <v>365</v>
+      </c>
+      <c r="C36" s="351"/>
+      <c r="D36" s="351"/>
+      <c r="E36" s="351"/>
+      <c r="F36" s="351"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="350" t="s">
-        <v>344</v>
-      </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="B37" s="354" t="s">
+        <v>343</v>
+      </c>
+      <c r="C37" s="354"/>
+      <c r="D37" s="354"/>
+      <c r="E37" s="354"/>
+      <c r="F37" s="354"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4560,13 +4590,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="352" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="352"/>
+      <c r="D40" s="352"/>
+      <c r="E40" s="352"/>
+      <c r="F40" s="352"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4586,13 +4616,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="352" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="352"/>
+      <c r="D43" s="352"/>
+      <c r="E43" s="352"/>
+      <c r="F43" s="352"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4621,13 +4651,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="352" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="352"/>
+      <c r="D47" s="352"/>
+      <c r="E47" s="352"/>
+      <c r="F47" s="352"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4643,21 +4673,21 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="352" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="352"/>
+      <c r="D50" s="352"/>
+      <c r="E50" s="352"/>
+      <c r="F50" s="352"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C51" s="317">
         <f>Normalized_FCF!C48</f>
-        <v>0</v>
+        <v>343835</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4668,7 +4698,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C52" s="317">
         <f>Normalized_FCF!C47</f>
@@ -4687,7 +4717,7 @@
       </c>
       <c r="C53" s="188">
         <f>Normalized_FCF!C12</f>
-        <v>-195728</v>
+        <v>148107</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4713,13 +4743,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="352" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="352"/>
+      <c r="D58" s="352"/>
+      <c r="E58" s="352"/>
+      <c r="F58" s="352"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4727,7 +4757,7 @@
       </c>
       <c r="C59" s="188">
         <f>Normalized_FCF!C14</f>
-        <v>47423.6875</v>
+        <v>-38535.0625</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4735,13 +4765,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
-        <v>343</v>
-      </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="B61" s="352" t="s">
+        <v>342</v>
+      </c>
+      <c r="C61" s="353"/>
+      <c r="D61" s="353"/>
+      <c r="E61" s="353"/>
+      <c r="F61" s="353"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4757,22 +4787,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="348" t="s">
-        <v>348</v>
-      </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="B64" s="351" t="s">
+        <v>347</v>
+      </c>
+      <c r="C64" s="351"/>
+      <c r="D64" s="351"/>
+      <c r="E64" s="351"/>
+      <c r="F64" s="351"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="348" t="s">
-        <v>367</v>
-      </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="B65" s="351" t="s">
+        <v>366</v>
+      </c>
+      <c r="C65" s="351"/>
+      <c r="D65" s="351"/>
+      <c r="E65" s="351"/>
+      <c r="F65" s="351"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4780,7 +4810,7 @@
       </c>
       <c r="C67" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>-206364</v>
+        <v>137471</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4793,7 +4823,7 @@
       </c>
       <c r="C68" s="188">
         <f>Normalized_FCF!C19</f>
-        <v>-143173.66759486249</v>
+        <v>114702.58240513749</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4802,16 +4832,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="252" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>-0.30360621563538431</v>
+        <v>0.24323199616686514</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="252" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
@@ -4820,7 +4850,7 @@
     </row>
     <row r="72" spans="1:6" ht="13.9">
       <c r="A72" s="247" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B72" s="36"/>
       <c r="C72" s="36"/>
@@ -4833,22 +4863,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="348" t="s">
-        <v>368</v>
-      </c>
-      <c r="C74" s="348"/>
-      <c r="D74" s="348"/>
-      <c r="E74" s="348"/>
-      <c r="F74" s="348"/>
+      <c r="B74" s="351" t="s">
+        <v>367</v>
+      </c>
+      <c r="C74" s="351"/>
+      <c r="D74" s="351"/>
+      <c r="E74" s="351"/>
+      <c r="F74" s="351"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="350" t="s">
+      <c r="B75" s="354" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="350"/>
-      <c r="D75" s="350"/>
-      <c r="E75" s="350"/>
-      <c r="F75" s="350"/>
+      <c r="C75" s="354"/>
+      <c r="D75" s="354"/>
+      <c r="E75" s="354"/>
+      <c r="F75" s="354"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4857,7 +4887,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
@@ -4866,7 +4896,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C79" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -4887,27 +4917,27 @@
     </row>
     <row r="82" spans="1:6">
       <c r="B82" s="326" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="348" t="s">
+      <c r="B83" s="351" t="s">
+        <v>368</v>
+      </c>
+      <c r="C83" s="351"/>
+      <c r="D83" s="351"/>
+      <c r="E83" s="351"/>
+      <c r="F83" s="351"/>
+    </row>
+    <row r="84" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B84" s="351" t="s">
         <v>369</v>
       </c>
-      <c r="C83" s="348"/>
-      <c r="D83" s="348"/>
-      <c r="E83" s="348"/>
-      <c r="F83" s="348"/>
-    </row>
-    <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="348" t="s">
-        <v>370</v>
-      </c>
-      <c r="C84" s="348"/>
-      <c r="D84" s="348"/>
-      <c r="E84" s="348"/>
-      <c r="F84" s="348"/>
+      <c r="C84" s="351"/>
+      <c r="D84" s="351"/>
+      <c r="E84" s="351"/>
+      <c r="F84" s="351"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4919,11 +4949,11 @@
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C87" s="248">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-86.14826368654029</v>
+        <v>69.017078912347984</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4932,7 +4962,7 @@
     </row>
     <row r="89" spans="1:6" ht="13.9">
       <c r="A89" s="247" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B89" s="36"/>
       <c r="C89" s="36"/>
@@ -4944,13 +4974,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="348" t="s">
-        <v>371</v>
-      </c>
-      <c r="C91" s="348"/>
-      <c r="D91" s="348"/>
-      <c r="E91" s="348"/>
-      <c r="F91" s="348"/>
+      <c r="B91" s="351" t="s">
+        <v>370</v>
+      </c>
+      <c r="C91" s="351"/>
+      <c r="D91" s="351"/>
+      <c r="E91" s="351"/>
+      <c r="F91" s="351"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4963,13 +4993,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="348" t="s">
-        <v>349</v>
-      </c>
-      <c r="C95" s="348"/>
-      <c r="D95" s="348"/>
-      <c r="E95" s="348"/>
-      <c r="F95" s="348"/>
+      <c r="B95" s="351" t="s">
+        <v>348</v>
+      </c>
+      <c r="C95" s="351"/>
+      <c r="D95" s="351"/>
+      <c r="E95" s="351"/>
+      <c r="F95" s="351"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -4986,7 +5016,7 @@
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C97" s="248">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -4999,7 +5029,7 @@
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="330" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C98" s="331">
         <f>BS!G30/BS!G27</f>
@@ -5008,7 +5038,7 @@
     </row>
     <row r="99" spans="2:6">
       <c r="B99" s="330" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C99" s="331">
         <f>BS!G31/BS!G27</f>
@@ -5017,7 +5047,7 @@
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="330" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C100" s="332">
         <f>BS!C50</f>
@@ -5048,7 +5078,7 @@
       </c>
       <c r="C104" s="188">
         <f>DCF!C8</f>
-        <v>6694703.2400284903</v>
+        <v>0</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5057,11 +5087,11 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C105" s="248">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>322.25873358617804</v>
+        <v>0</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>Market_currency</f>
@@ -5088,7 +5118,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C109" s="248">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5100,21 +5130,21 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="348" t="s">
-        <v>372</v>
-      </c>
-      <c r="C111" s="348"/>
-      <c r="D111" s="348"/>
-      <c r="E111" s="348"/>
-      <c r="F111" s="348"/>
+      <c r="B111" s="351" t="s">
+        <v>371</v>
+      </c>
+      <c r="C111" s="351"/>
+      <c r="D111" s="351"/>
+      <c r="E111" s="351"/>
+      <c r="F111" s="351"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C113" s="248">
         <f>DCF!C12</f>
-        <v>-118.69228650791112</v>
+        <v>-285.78567749520096</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
@@ -5123,7 +5153,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="330" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C114" s="248">
         <f>BS!D47</f>
@@ -5136,7 +5166,7 @@
     </row>
     <row r="116" spans="1:6" ht="13.9">
       <c r="A116" s="247" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B116" s="36"/>
       <c r="C116" s="36"/>
@@ -5145,13 +5175,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="349" t="s">
-        <v>373</v>
-      </c>
-      <c r="C118" s="349"/>
-      <c r="D118" s="349"/>
-      <c r="E118" s="349"/>
-      <c r="F118" s="349"/>
+      <c r="B118" s="352" t="s">
+        <v>372</v>
+      </c>
+      <c r="C118" s="352"/>
+      <c r="D118" s="352"/>
+      <c r="E118" s="352"/>
+      <c r="F118" s="352"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="258" t="s">
@@ -5177,15 +5207,15 @@
       </c>
       <c r="C121" s="254">
         <f>DCF!C74</f>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="D121" s="255">
         <f>DCF!D74</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E121" s="256" t="str">
         <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>-150.64 CNY</v>
+        <v>-181.75 CNY</v>
       </c>
       <c r="F121" s="257">
         <f>DCF!F74</f>
@@ -5199,15 +5229,15 @@
       </c>
       <c r="C122" s="243">
         <f>DCF!C75</f>
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="D122" s="244">
         <f>DCF!D75</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E122" s="245" t="str">
         <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>-130.37 CNY</v>
+        <v>-221.93 CNY</v>
       </c>
       <c r="F122" s="246">
         <f>DCF!F75</f>
@@ -5221,15 +5251,15 @@
       </c>
       <c r="C123" s="243">
         <f>DCF!C76</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D123" s="244">
         <f>DCF!D76</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E123" s="245" t="str">
         <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>-124.25 CNY</v>
+        <v>-250.38 CNY</v>
       </c>
       <c r="F123" s="246">
         <f>DCF!F76</f>
@@ -5243,15 +5273,15 @@
       </c>
       <c r="C124" s="243">
         <f>DCF!C77</f>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D124" s="244">
         <f>DCF!D77</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E124" s="245" t="str">
         <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>-118.69 CNY</v>
+        <v>-270.84 CNY</v>
       </c>
       <c r="F124" s="246">
         <f>DCF!F77</f>
@@ -5269,11 +5299,11 @@
       </c>
       <c r="D125" s="244">
         <f>DCF!D78</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E125" s="245" t="str">
         <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>-118.69 CNY</v>
+        <v>-285.79 CNY</v>
       </c>
       <c r="F125" s="246">
         <f>DCF!F78</f>
@@ -5286,7 +5316,7 @@
       </c>
       <c r="C127" s="241">
         <f>Scenarios!C60</f>
-        <v>-125.39563243722989</v>
+        <v>21.752920556327282</v>
       </c>
       <c r="D127" s="236" t="str">
         <f>Market_currency</f>
@@ -5294,17 +5324,17 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="353" t="s">
-        <v>376</v>
-      </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="B129" s="355" t="s">
+        <v>375</v>
+      </c>
+      <c r="C129" s="355"/>
+      <c r="D129" s="355"/>
+      <c r="E129" s="355"/>
+      <c r="F129" s="355"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B131" s="36"/>
       <c r="C131" s="36"/>
@@ -5313,22 +5343,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="351" t="s">
+      <c r="B133" s="356" t="s">
+        <v>373</v>
+      </c>
+      <c r="C133" s="356"/>
+      <c r="D133" s="356"/>
+      <c r="E133" s="356"/>
+      <c r="F133" s="356"/>
+    </row>
+    <row r="134" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B134" s="351" t="s">
         <v>374</v>
       </c>
-      <c r="C133" s="351"/>
-      <c r="D133" s="351"/>
-      <c r="E133" s="351"/>
-      <c r="F133" s="351"/>
-    </row>
-    <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="348" t="s">
-        <v>375</v>
-      </c>
-      <c r="C134" s="348"/>
-      <c r="D134" s="348"/>
-      <c r="E134" s="348"/>
-      <c r="F134" s="348"/>
+      <c r="C134" s="351"/>
+      <c r="D134" s="351"/>
+      <c r="E134" s="351"/>
+      <c r="F134" s="351"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5368,7 +5398,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="234" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C140" s="268" t="str">
         <f>C11</f>
@@ -5381,7 +5411,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C141" s="331">
         <f>F29</f>
@@ -5405,7 +5435,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C82</f>
-        <v>-45.698116777416153</v>
+        <v>7.9274491823350175</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5414,7 +5444,7 @@
       </c>
       <c r="C144" s="239">
         <f>Scenarios!C83</f>
-        <v>-44.013860217649388</v>
+        <v>9.6117057421017815</v>
       </c>
       <c r="D144" s="335" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
@@ -5423,7 +5453,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="286" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C145" s="333" t="str">
         <f>Market_currency</f>
@@ -5440,17 +5470,17 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.64900005397172267</v>
+        <v>0.55814182664745582</v>
       </c>
     </row>
     <row r="148" spans="2:4">
       <c r="B148" s="234" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C149" s="331">
         <f>Scenarios!C90</f>
@@ -5474,7 +5504,7 @@
       </c>
       <c r="C151" s="240">
         <f>Scenarios!C92</f>
-        <v>-69.056238428122782</v>
+        <v>11.97948317057776</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5483,7 +5513,7 @@
       </c>
       <c r="C152" s="239">
         <f>Scenarios!C93</f>
-        <v>-66.891462521769384</v>
+        <v>14.144259076931155</v>
       </c>
       <c r="D152" s="335" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5492,7 +5522,7 @@
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="286" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C153" s="333" t="str">
         <f>Market_currency</f>
@@ -5509,17 +5539,17 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.46655667967340342</v>
+        <v>0.34977654884061038</v>
       </c>
     </row>
     <row r="156" spans="2:4">
       <c r="B156" s="234" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
@@ -5543,16 +5573,16 @@
       </c>
       <c r="C159" s="240">
         <f>Scenarios!C98</f>
-        <v>-99.543095911787674</v>
+        <v>17.268169673963001</v>
       </c>
     </row>
     <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
-        <v>-96.811373105304924</v>
+        <v>19.999892480445755</v>
       </c>
       <c r="D160" s="335" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
@@ -5561,7 +5591,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="B161" s="286" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C161" s="333" t="str">
         <f>Market_currency</f>
@@ -5578,17 +5608,17 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>0.22795259114174948</v>
+        <v>8.0588170739750331E-2</v>
       </c>
     </row>
     <row r="164" spans="1:6">
       <c r="B164" s="234" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C165" s="92">
         <f>F32</f>
@@ -5612,16 +5642,16 @@
       </c>
       <c r="C167" s="240">
         <f>Scenarios!C104</f>
-        <v>-89.254134330890878</v>
+        <v>15.483299184248073</v>
       </c>
     </row>
     <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
-        <v>-86.708193186576011</v>
+        <v>18.029240328562945</v>
       </c>
       <c r="D168" s="335" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
@@ -5630,7 +5660,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="B169" s="286" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C169" s="333" t="str">
         <f>Market_currency</f>
@@ -5647,12 +5677,12 @@
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.34568602529218084</v>
+        <v>0.17104839072722289</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
       <c r="A172" s="247" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B172" s="36"/>
       <c r="C172" s="36"/>
@@ -5661,113 +5691,102 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="355" t="s">
-        <v>382</v>
-      </c>
-      <c r="C174" s="348"/>
-      <c r="D174" s="348"/>
-      <c r="E174" s="348"/>
-      <c r="F174" s="348"/>
+      <c r="B174" s="350" t="s">
+        <v>381</v>
+      </c>
+      <c r="C174" s="351"/>
+      <c r="D174" s="351"/>
+      <c r="E174" s="351"/>
+      <c r="F174" s="351"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="352" t="s">
-        <v>386</v>
-      </c>
-      <c r="C177" s="352"/>
-      <c r="D177" s="352"/>
-      <c r="E177" s="352"/>
-      <c r="F177" s="352"/>
+      <c r="B177" s="353" t="s">
+        <v>385</v>
+      </c>
+      <c r="C177" s="353"/>
+      <c r="D177" s="353"/>
+      <c r="E177" s="353"/>
+      <c r="F177" s="353"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="179" spans="2:6">
       <c r="B179" s="238" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="180" spans="2:6">
       <c r="B180" s="238" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="349" t="s">
-        <v>387</v>
-      </c>
-      <c r="C183" s="349"/>
-      <c r="D183" s="349"/>
-      <c r="E183" s="349"/>
-      <c r="F183" s="349"/>
+      <c r="B183" s="352" t="s">
+        <v>386</v>
+      </c>
+      <c r="C183" s="352"/>
+      <c r="D183" s="352"/>
+      <c r="E183" s="352"/>
+      <c r="F183" s="352"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="354" t="s">
+      <c r="B186" s="349" t="s">
+        <v>387</v>
+      </c>
+      <c r="C186" s="349"/>
+      <c r="D186" s="349"/>
+      <c r="E186" s="349"/>
+      <c r="F186" s="349"/>
+    </row>
+    <row r="187" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B187" s="349" t="s">
         <v>388</v>
       </c>
-      <c r="C186" s="354"/>
-      <c r="D186" s="354"/>
-      <c r="E186" s="354"/>
-      <c r="F186" s="354"/>
-    </row>
-    <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="354" t="s">
-        <v>389</v>
-      </c>
-      <c r="C187" s="354"/>
-      <c r="D187" s="354"/>
-      <c r="E187" s="354"/>
-      <c r="F187" s="354"/>
+      <c r="C187" s="349"/>
+      <c r="D187" s="349"/>
+      <c r="E187" s="349"/>
+      <c r="F187" s="349"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="190" spans="2:6">
       <c r="B190" s="238" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="191" spans="2:6">
       <c r="B191" s="238" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="192" spans="2:6">
       <c r="B192" s="238" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5784,6 +5803,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -5796,7 +5826,7 @@
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
       <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6356,7 +6386,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C22" s="181">
         <v>-237258</v>
@@ -6392,7 +6422,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C23" s="181">
         <v>23438</v>
@@ -6428,7 +6458,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C24" s="181">
         <v>194894</v>
@@ -7756,7 +7786,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -9138,7 +9168,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F45" s="283" t="s">
         <v>59</v>
@@ -9344,7 +9374,7 @@
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F65" s="283" t="s">
         <v>59</v>
@@ -9360,7 +9390,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>6694703.2400284903</v>
+        <v>0</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9411,7 +9441,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="282" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C72" s="259" t="s">
         <v>96</v>
@@ -9423,7 +9453,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9434,12 +9464,12 @@
         <v>-7000.4599952516664</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="284" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C74" s="285">
         <f>-$C$66/C73</f>
@@ -9450,33 +9480,33 @@
         <v>962.32333369084779</v>
       </c>
       <c r="F74" s="280" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C75" s="289"/>
       <c r="D75" s="288">
         <f>MAX(-D73*D76,G5)</f>
-        <v>42002.75997151</v>
+        <v>6736706</v>
       </c>
       <c r="F75" s="280" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="286" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C76" s="287"/>
       <c r="D76" s="322">
-        <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
-        <v>6</v>
+        <f>IF(valuation_method="DCF",IF(D74&lt;=3,1,IF(D74&gt;18,6,2)),-C66/D73)</f>
+        <v>962.32333369084779</v>
       </c>
       <c r="F76" s="280" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9552,7 +9582,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9563,15 +9593,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="D85" s="268" t="s">
         <v>293</v>
-      </c>
-      <c r="D85" s="268" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="265" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C86" s="188">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9588,15 +9618,15 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="265" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C87" s="188">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>6694703.2400284903</v>
+        <v>0</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>322.25873358617804</v>
+        <v>0</v>
       </c>
       <c r="E87" s="267" t="str">
         <f>Market_currency</f>
@@ -9622,15 +9652,15 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-676079.65997150959</v>
+        <v>-7370782.9000000004</v>
       </c>
       <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
-        <v>-32.544022821370888</v>
+        <v>-354.80275640754894</v>
       </c>
       <c r="E89" s="267" t="str">
         <f>Market_currency</f>
@@ -10210,48 +10240,48 @@
       </c>
       <c r="C12" s="191">
         <f>C50</f>
-        <v>-195728</v>
+        <v>148107</v>
       </c>
       <c r="E12" s="298"/>
       <c r="G12" s="191">
         <f>G50</f>
-        <v>-195728</v>
+        <v>148107</v>
       </c>
       <c r="H12" s="191">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>-202576</v>
+        <v>146503</v>
       </c>
       <c r="I12" s="191">
         <f t="shared" si="6"/>
-        <v>-183473</v>
+        <v>145273</v>
       </c>
       <c r="J12" s="191">
         <f t="shared" si="6"/>
-        <v>-169479</v>
+        <v>145679</v>
       </c>
       <c r="K12" s="191">
         <f t="shared" si="6"/>
-        <v>-159963</v>
+        <v>143515</v>
       </c>
       <c r="L12" s="191">
         <f t="shared" si="6"/>
-        <v>-166689</v>
+        <v>102988</v>
       </c>
       <c r="M12" s="191">
         <f t="shared" si="6"/>
-        <v>-174921</v>
+        <v>95657</v>
       </c>
       <c r="N12" s="191">
         <f t="shared" si="6"/>
-        <v>-164193</v>
+        <v>88451</v>
       </c>
       <c r="O12" s="191">
         <f t="shared" si="6"/>
-        <v>-123960</v>
+        <v>112319</v>
       </c>
       <c r="P12" s="191">
         <f t="shared" si="6"/>
-        <v>-136138</v>
+        <v>119834</v>
       </c>
       <c r="Q12" s="191" t="str">
         <f t="shared" si="6"/>
@@ -10265,48 +10295,48 @@
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
-        <v>-189694.75</v>
+        <v>154140.25</v>
       </c>
       <c r="E13" s="298"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>-196449</v>
+        <v>147386</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>-203761</v>
+        <v>145318</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>-173964</v>
+        <v>154782</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>-152949</v>
+        <v>162209</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
-        <v>-151504</v>
+        <v>151974</v>
       </c>
       <c r="L13" s="184">
         <f t="shared" si="7"/>
-        <v>-137315</v>
+        <v>132362</v>
       </c>
       <c r="M13" s="184">
         <f t="shared" si="7"/>
-        <v>-156260</v>
+        <v>114318</v>
       </c>
       <c r="N13" s="184">
         <f t="shared" si="7"/>
-        <v>-152324</v>
+        <v>100320</v>
       </c>
       <c r="O13" s="184">
         <f t="shared" si="7"/>
-        <v>-121621</v>
+        <v>114658</v>
       </c>
       <c r="P13" s="184">
         <f t="shared" si="7"/>
-        <v>-147902</v>
+        <v>108070</v>
       </c>
       <c r="Q13" s="184" t="str">
         <f t="shared" si="7"/>
@@ -10320,7 +10350,7 @@
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>47423.6875</v>
+        <v>-38535.0625</v>
       </c>
       <c r="E14" s="298"/>
       <c r="G14" s="191">
@@ -10432,50 +10462,50 @@
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
-        <v>-143173.66759486249</v>
+        <v>114702.58240513749</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="306"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>-206364</v>
+        <v>137471</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>-210974</v>
+        <v>138105</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>-188808</v>
+        <v>139938</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>-165579</v>
+        <v>149579</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
-        <v>-161515</v>
+        <v>141963</v>
       </c>
       <c r="L16" s="184">
         <f t="shared" si="8"/>
-        <v>-145950</v>
+        <v>123727</v>
       </c>
       <c r="M16" s="184">
         <f t="shared" si="8"/>
-        <v>-163717</v>
+        <v>106861</v>
       </c>
       <c r="N16" s="184">
         <f t="shared" si="8"/>
-        <v>-159877</v>
+        <v>92767</v>
       </c>
       <c r="O16" s="184">
         <f t="shared" si="8"/>
-        <v>-131696</v>
+        <v>104583</v>
       </c>
       <c r="P16" s="184">
         <f t="shared" si="8"/>
-        <v>-160939</v>
+        <v>95033</v>
       </c>
       <c r="Q16" s="184" t="str">
         <f t="shared" si="8"/>
@@ -10493,7 +10523,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="297" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10518,7 +10548,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="297" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10540,50 +10570,50 @@
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
-        <v>-143173.66759486249</v>
+        <v>114702.58240513749</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="295"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>-206364</v>
+        <v>137471</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>-210974</v>
+        <v>138105</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>-188808</v>
+        <v>139938</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>-165579</v>
+        <v>149579</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
-        <v>-161515</v>
+        <v>141963</v>
       </c>
       <c r="L19" s="186">
         <f t="shared" si="9"/>
-        <v>-145950</v>
+        <v>123727</v>
       </c>
       <c r="M19" s="186">
         <f t="shared" si="9"/>
-        <v>-163717</v>
+        <v>106861</v>
       </c>
       <c r="N19" s="186">
         <f t="shared" si="9"/>
-        <v>-159877</v>
+        <v>92767</v>
       </c>
       <c r="O19" s="186">
         <f t="shared" si="9"/>
-        <v>-131696</v>
+        <v>104583</v>
       </c>
       <c r="P19" s="186">
         <f t="shared" si="9"/>
-        <v>-160939</v>
+        <v>95033</v>
       </c>
       <c r="Q19" s="186" t="str">
         <f t="shared" si="9"/>
@@ -10846,7 +10876,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="296" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10906,7 +10936,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="296" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11030,7 +11060,7 @@
         <v>-61984.75</v>
       </c>
       <c r="E33" s="296" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -11088,7 +11118,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="296" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11396,48 +11426,48 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="295" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>-4.9015266048694571E-2</v>
+        <v>6.5331849700785691E-2</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>-3.2758967614018385E-2</v>
+        <v>4.5933745303403571E-2</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>-7.936699547032719E-2</v>
+        <v>8.9202878887725962E-2</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>-7.5149232750786207E-2</v>
+        <v>7.0859200167684905E-2</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>-5.9113950786777905E-2</v>
+        <v>5.893113295695316E-2</v>
       </c>
       <c r="L43" s="6">
         <f t="shared" si="18"/>
-        <v>-5.6810982048574446E-2</v>
+        <v>5.8936854988591893E-2</v>
       </c>
       <c r="M43" s="6">
         <f t="shared" si="18"/>
-        <v>-4.3722001791885318E-2</v>
+        <v>5.9763116919470248E-2</v>
       </c>
       <c r="N43" s="6">
         <f t="shared" si="18"/>
-        <v>-4.6072844725716239E-2</v>
+        <v>6.9956140350877188E-2</v>
       </c>
       <c r="O43" s="6">
         <f t="shared" si="18"/>
-        <v>-7.8917292243938134E-2</v>
+        <v>8.370981527673603E-2</v>
       </c>
       <c r="P43" s="6">
         <f t="shared" si="18"/>
-        <v>-8.5150978350529399E-2</v>
+        <v>0.11653557879152401</v>
       </c>
       <c r="Q43" s="6" t="str">
         <f t="shared" si="18"/>
@@ -11535,52 +11565,52 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
-        <v>0</v>
+        <v>343835</v>
       </c>
       <c r="E48" s="298"/>
       <c r="G48" s="323">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>0</v>
+        <v>343835</v>
       </c>
       <c r="H48" s="323">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>0</v>
+        <v>349079</v>
       </c>
       <c r="I48" s="323">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>328746</v>
       </c>
       <c r="J48" s="323">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>315158</v>
       </c>
       <c r="K48" s="323">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>303478</v>
       </c>
       <c r="L48" s="323">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>269677</v>
       </c>
       <c r="M48" s="323">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>270578</v>
       </c>
       <c r="N48" s="323">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>252644</v>
       </c>
       <c r="O48" s="323">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>236279</v>
       </c>
       <c r="P48" s="323">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>255972</v>
       </c>
       <c r="Q48" s="323" t="str">
         <f t="shared" si="19"/>
@@ -11590,11 +11620,11 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="318" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C49" s="319">
         <f>BS!$C$66*C53</f>
-        <v>0</v>
+        <v>343835</v>
       </c>
       <c r="D49" s="320"/>
       <c r="E49" s="321"/>
@@ -11651,48 +11681,48 @@
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
-        <v>-195728</v>
+        <v>148107</v>
       </c>
       <c r="E50" s="298"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>-195728</v>
+        <v>148107</v>
       </c>
       <c r="H50" s="184">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>-202576</v>
+        <v>146503</v>
       </c>
       <c r="I50" s="184">
         <f t="shared" si="20"/>
-        <v>-183473</v>
+        <v>145273</v>
       </c>
       <c r="J50" s="184">
         <f t="shared" si="20"/>
-        <v>-169479</v>
+        <v>145679</v>
       </c>
       <c r="K50" s="184">
         <f t="shared" si="20"/>
-        <v>-159963</v>
+        <v>143515</v>
       </c>
       <c r="L50" s="184">
         <f t="shared" si="20"/>
-        <v>-166689</v>
+        <v>102988</v>
       </c>
       <c r="M50" s="184">
         <f t="shared" si="20"/>
-        <v>-174921</v>
+        <v>95657</v>
       </c>
       <c r="N50" s="184">
         <f t="shared" si="20"/>
-        <v>-164193</v>
+        <v>88451</v>
       </c>
       <c r="O50" s="184">
         <f t="shared" si="20"/>
-        <v>-123960</v>
+        <v>112319</v>
       </c>
       <c r="P50" s="184">
         <f t="shared" si="20"/>
-        <v>-136138</v>
+        <v>119834</v>
       </c>
       <c r="Q50" s="184" t="str">
         <f t="shared" si="20"/>
@@ -11719,10 +11749,11 @@
         <v>89</v>
       </c>
       <c r="C53" s="87">
-        <v>0</v>
+        <f>G53</f>
+        <v>5.1039038960584003E-2</v>
       </c>
       <c r="E53" s="295" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11749,7 +11780,7 @@
         <v>2.0566860106198924E-2</v>
       </c>
       <c r="E54" s="295" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -12064,7 +12095,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="296" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12625,7 +12656,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="296" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12737,50 +12768,50 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>2.8775912258519805</v>
+        <v>2.1774677291305244</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="295"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>3.1625141379867507</v>
+        <v>2.3930683470673775</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>3.2668806141044042</v>
+        <v>2.3626086535825443</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>2.4520936075805566</v>
+        <v>1.9415554040869787</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>2.3105521472392638</v>
+        <v>1.9860804362644853</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>2.7802245550611793</v>
+        <v>2.4943513626251392</v>
       </c>
       <c r="L80" s="6">
         <f t="shared" si="31"/>
-        <v>2.1771197952040122</v>
+        <v>1.3451230343242255</v>
       </c>
       <c r="M80" s="6">
         <f t="shared" si="31"/>
-        <v>2.8571591911404397</v>
+        <v>1.5624612067557413</v>
       </c>
       <c r="N80" s="6">
         <f t="shared" si="31"/>
-        <v>3.2481948208668818</v>
+        <v>1.7498071178460504</v>
       </c>
       <c r="O80" s="6">
         <f t="shared" si="31"/>
-        <v>3.1724420330654657</v>
+        <v>2.87452014127041</v>
       </c>
       <c r="P80" s="6">
         <f t="shared" si="31"/>
-        <v>6.3146713669465191</v>
+        <v>5.5584210770443896</v>
       </c>
       <c r="Q80" s="6" t="str">
         <f t="shared" si="31"/>
@@ -12794,50 +12825,50 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>-2.7888904407656798</v>
+        <v>2.2661685142168251</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="295"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>-3.1741638390693163</v>
+        <v>2.3814186459848119</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>-3.2859907432792013</v>
+        <v>2.3434985244077473</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>-2.3250070165590793</v>
+        <v>2.068641995108456</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>-2.08519427402863</v>
+        <v>2.2114383094751191</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>-2.6332035595105672</v>
+        <v>2.6413723581757509</v>
       </c>
       <c r="L81" s="65">
         <f t="shared" si="32"/>
-        <v>-1.7934669035055639</v>
+        <v>1.7287759260226738</v>
       </c>
       <c r="M81" s="65">
         <f t="shared" si="32"/>
-        <v>-2.5523504622521318</v>
+        <v>1.8672699356440494</v>
       </c>
       <c r="N81" s="65">
         <f t="shared" si="32"/>
-        <v>-3.0133929454588615</v>
+        <v>1.9846089932540703</v>
       </c>
       <c r="O81" s="65">
         <f t="shared" si="32"/>
-        <v>-3.1125812560782107</v>
+        <v>2.934380918257665</v>
       </c>
       <c r="P81" s="65">
         <f t="shared" si="32"/>
-        <v>-6.8603367503130945</v>
+        <v>5.0127556936778142</v>
       </c>
       <c r="Q81" s="65" t="str">
         <f t="shared" si="32"/>
@@ -12851,7 +12882,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>0.69722261019141996</v>
+        <v>0.56654212855420627</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="295"/>
@@ -12966,50 +12997,50 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>2.10493792223915</v>
+        <v>1.6863562939977286</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="295"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>3.3343674260785265</v>
+        <v>2.2212150589756017</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>3.4023125675305197</v>
+        <v>2.2271767001564289</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>2.5233952127019768</v>
+        <v>1.8702537989655588</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>2.2573824130879347</v>
+        <v>2.0392501704158148</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>2.8071989710789764</v>
+        <v>2.4673769466073416</v>
       </c>
       <c r="L84" s="65">
         <f t="shared" si="35"/>
-        <v>1.9062483673789248</v>
+        <v>1.615994462149313</v>
       </c>
       <c r="M84" s="65">
         <f t="shared" si="35"/>
-        <v>2.6741530822253439</v>
+        <v>1.7454673156708373</v>
       </c>
       <c r="N84" s="65">
         <f t="shared" si="35"/>
-        <v>3.1628123207185106</v>
+        <v>1.8351896179944212</v>
       </c>
       <c r="O84" s="65">
         <f t="shared" si="35"/>
-        <v>3.3704253467779086</v>
+        <v>2.6765368275579671</v>
       </c>
       <c r="P84" s="65">
         <f t="shared" si="35"/>
-        <v>7.4650493993227887</v>
+        <v>4.40804304466812</v>
       </c>
       <c r="Q84" s="65" t="str">
         <f t="shared" si="35"/>
@@ -13073,50 +13104,50 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>2.10493792223915</v>
+        <v>1.6863562939977286</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="295"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>3.3343674260785265</v>
+        <v>2.2212150589756017</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>3.4023125675305197</v>
+        <v>2.2271767001564289</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>2.5233952127019768</v>
+        <v>1.8702537989655588</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>2.2573824130879347</v>
+        <v>2.0392501704158148</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>2.8071989710789764</v>
+        <v>2.4673769466073416</v>
       </c>
       <c r="L87" s="65">
         <f t="shared" si="36"/>
-        <v>1.9062483673789248</v>
+        <v>1.615994462149313</v>
       </c>
       <c r="M87" s="65">
         <f t="shared" si="36"/>
-        <v>2.6741530822253439</v>
+        <v>1.7454673156708373</v>
       </c>
       <c r="N87" s="65">
         <f t="shared" si="36"/>
-        <v>3.1628123207185106</v>
+        <v>1.8351896179944212</v>
       </c>
       <c r="O87" s="65">
         <f t="shared" si="36"/>
-        <v>3.3704253467779086</v>
+        <v>2.6765368275579671</v>
       </c>
       <c r="P87" s="65">
         <f t="shared" si="36"/>
-        <v>7.4650493993227887</v>
+        <v>4.40804304466812</v>
       </c>
       <c r="Q87" s="65" t="str">
         <f t="shared" si="36"/>
@@ -13253,12 +13284,12 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>-0.15380460885679076</v>
+        <v>0.19198146616473824</v>
       </c>
       <c r="E92" s="298"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>-0.10670838878399334</v>
+        <v>0.16018483856973473</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
@@ -13304,7 +13335,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13445,46 +13476,46 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-3.4381697030781533E-2</v>
+        <v>4.5826944214511611E-2</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="295"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-3.5885179205049078E-2</v>
+        <v>1.423085921909184E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>0.17128256420868682</v>
+        <v>-6.1144060678890333E-2</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>0.13739874075672276</v>
+        <v>-4.5786608634539427E-2</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>9.5377019748652536E-3</v>
+        <v>6.7347046205271877E-2</v>
       </c>
       <c r="K97" s="6">
         <f t="shared" si="41"/>
-        <v>0.10333175545279105</v>
+        <v>0.14816941418231822</v>
       </c>
       <c r="L97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.12124024062460004</v>
+        <v>0.15784041008415128</v>
       </c>
       <c r="M97" s="6">
         <f t="shared" si="41"/>
-        <v>2.5839657572017449E-2</v>
+        <v>0.13953349282296656</v>
       </c>
       <c r="N97" s="6">
         <f t="shared" si="41"/>
-        <v>0.25244817917958251</v>
+        <v>-0.12505014913917911</v>
       </c>
       <c r="O97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.17769198523346541</v>
+        <v>6.0960488572221694E-2</v>
       </c>
       <c r="P97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -13998,7 +14029,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="298"/>
@@ -14050,49 +14081,49 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="298"/>
       <c r="G114" s="328">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.1497063441297901</v>
+        <v>-1.7258767303649496</v>
       </c>
       <c r="H114" s="328">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>-2.055310133002171</v>
+        <v>3.1397632236341915</v>
       </c>
       <c r="I114" s="328">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.825065675183255</v>
+        <v>-2.4624262173248153</v>
       </c>
       <c r="J114" s="328">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>2.3539881265136278</v>
+        <v>-2.6057869085901095</v>
       </c>
       <c r="K114" s="328">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>0.21191839767204285</v>
+        <v>-0.24110507667490824</v>
       </c>
       <c r="L114" s="328">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>4.0288386433710173</v>
+        <v>-4.752471166358192</v>
       </c>
       <c r="M114" s="328">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>2.175088720169561</v>
+        <v>-3.3323569871141014</v>
       </c>
       <c r="N114" s="328">
         <f>IF(N$4="","",Data!J$22/N19)</f>
-        <v>1.0172945451816084</v>
+        <v>-1.7532312136859012</v>
       </c>
       <c r="O114" s="328">
         <f>IF(O$4="","",Data!K$22/O19)</f>
-        <v>-1.5415578301542947</v>
+        <v>1.941204593480776</v>
       </c>
       <c r="P114" s="328">
         <f>IF(P$4="","",Data!L$22/P19)</f>
-        <v>-5.0869770534177547</v>
+        <v>8.6148285332463459</v>
       </c>
       <c r="Q114" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
@@ -14164,48 +14195,48 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>-2.7888904407656798</v>
+        <v>2.2661685142168251</v>
       </c>
       <c r="E117" s="298"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>-3.1741638390693163</v>
+        <v>2.3814186459848119</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>-3.2859907432792013</v>
+        <v>2.3434985244077473</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>-2.3250070165590793</v>
+        <v>2.068641995108456</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>-2.08519427402863</v>
+        <v>2.2114383094751191</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
-        <v>-2.6332035595105672</v>
+        <v>2.6413723581757509</v>
       </c>
       <c r="L117" s="23">
         <f t="shared" si="45"/>
-        <v>-1.7934669035055639</v>
+        <v>1.7287759260226738</v>
       </c>
       <c r="M117" s="23">
         <f t="shared" si="45"/>
-        <v>-2.5523504622521318</v>
+        <v>1.8672699356440494</v>
       </c>
       <c r="N117" s="23">
         <f t="shared" si="45"/>
-        <v>-3.0133929454588615</v>
+        <v>1.9846089932540703</v>
       </c>
       <c r="O117" s="23">
         <f t="shared" si="45"/>
-        <v>-3.1125812560782107</v>
+        <v>2.934380918257665</v>
       </c>
       <c r="P117" s="23">
         <f t="shared" si="45"/>
-        <v>-6.8603367503130945</v>
+        <v>5.0127556936778142</v>
       </c>
       <c r="Q117" s="23" t="str">
         <f t="shared" si="45"/>
@@ -14450,50 +14481,50 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>-6.8918610949232235</v>
+        <v>5.5213663129878379</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>-9.9336145178400823</v>
+        <v>6.6173553593746677</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>-10.15552319826517</v>
+        <v>6.6478738199797665</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>-9.088532350043371</v>
+        <v>6.7361077920446659</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>-7.9703725371161784</v>
+        <v>7.2001905660095833</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>-7.7747463164551034</v>
+        <v>6.8335839477628442</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>-7.0255036676879694</v>
+        <v>5.9557690461941029</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>-7.8807426102286486</v>
+        <v>5.1439009759013636</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>-7.6958989371630659</v>
+        <v>4.4654669321028422</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>-6.3393678041783819</v>
+        <v>5.0342463177650627</v>
       </c>
       <c r="P124" s="178">
         <f t="shared" si="49"/>
-        <v>-7.7470197654952662</v>
+        <v>4.5745439537608137</v>
       </c>
       <c r="Q124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14507,50 +14538,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>-0.30360621563538431</v>
+        <v>0.24323199616686514</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>-0.43760416378150141</v>
+        <v>0.29151345195483119</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>-0.44737987657555817</v>
+        <v>0.29285787753214831</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>-0.40037587445124984</v>
+        <v>0.29674483665395007</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>-0.35111773291260701</v>
+        <v>0.31718901171848385</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>-0.34249983772929971</v>
+        <v>0.30103894043008123</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>-0.30949355364264186</v>
+        <v>0.26236868044907941</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>-0.34716927798364094</v>
+        <v>0.2266035672203244</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>-0.33902638489705139</v>
+        <v>0.19671660493845119</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>-0.27926730414882739</v>
+        <v>0.22177296554031115</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>-0.3412784037663113</v>
+        <v>0.20152176007756889</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14559,7 +14590,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15350,7 +15381,7 @@
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
-        <v>-143173.66759486249</v>
+        <v>114702.58240513749</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15360,7 +15391,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C86</f>
+        <f>Terminal_Growth</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15370,7 +15401,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C80</f>
+        <f>Equity_Cost</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15382,16 +15413,16 @@
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>-1789670.8449357811</v>
+        <v>1433782.2800642187</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="357" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="357"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15406,8 +15437,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="357"/>
+      <c r="F7" s="357"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15416,14 +15447,14 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>6694703.2400284903</v>
+        <v>0</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="357"/>
+      <c r="F8" s="357"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15438,8 +15469,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="357"/>
+      <c r="F9" s="357"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15448,7 +15479,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>-2465750.50490729</v>
+        <v>-5937000.6199357808</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15476,7 +15507,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>-118.69228650791112</v>
+        <v>-285.78567749520096</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15509,7 +15540,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>4.6574870890079501E-2</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -15519,7 +15550,7 @@
       </c>
       <c r="C17" s="163">
         <f>Scenarios!C64</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H17" s="121"/>
     </row>
@@ -15529,7 +15560,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>-132.51771555894882</v>
+        <v>-247.31492181539969</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15564,11 +15595,11 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>-149841.96267795237</v>
+        <v>119578.62549648884</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -15576,7 +15607,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>-138742.55803514106</v>
+        <v>110720.94953378594</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -15586,11 +15617,11 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>-156820.8327435941</v>
+        <v>124661.95072334378</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -15598,7 +15629,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>-134448.58774313622</v>
+        <v>106877.52976967058</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -15608,11 +15639,11 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>-164124.74278150176</v>
+        <v>129961.36971490533</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -15620,7 +15651,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>-130287.51236909845</v>
+        <v>103167.5253668341</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -15630,11 +15661,11 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>-171768.83148641774</v>
+        <v>135486.06868552361</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -15642,7 +15673,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>-126255.21892248042</v>
+        <v>99586.305121890575</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -15652,11 +15683,11 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>-179768.94263583748</v>
+        <v>141245.6243584289</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -15664,7 +15695,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>-122347.72170647563</v>
+        <v>96129.398592888087</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -15674,11 +15705,11 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>-188141.65792914771</v>
+        <v>147250.020566388</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
@@ -15686,7 +15717,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>-118561.1583783797</v>
+        <v>92792.490518850202</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -15696,11 +15727,11 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>-196904.33135624332</v>
+        <v>153509.66555805926</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
@@ -15708,7 +15739,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>-114891.7861318806</v>
+        <v>89571.415433029979</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -15718,11 +15749,11 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>-206075.12516685776</v>
+        <v>160035.41004004664</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
@@ -15730,7 +15761,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>-111335.97799750327</v>
+        <v>86462.152463152292</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -15740,11 +15771,11 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>-215673.04751516116</v>
+        <v>166838.56598592701</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
@@ -15752,7 +15783,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>-107890.21925755346</v>
+        <v>83460.820312153766</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -15762,11 +15793,11 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>-225717.99185764979</v>
+        <v>173930.92624485528</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
@@ -15774,7 +15805,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>-104551.10397201516</v>
+        <v>80563.672413154462</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15784,19 +15815,19 @@
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>181324.78498373734</v>
       </c>
       <c r="D31" s="139">
         <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
-        <v>0</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E31" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.42888285933767062</v>
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>77767.092252613584</v>
       </c>
       <c r="H31" s="121"/>
     </row>
@@ -15806,19 +15837,19 @@
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>189032.95899840642</v>
       </c>
       <c r="D32" s="139">
         <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
-        <v>0</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E32" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.39711375864599124</v>
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>75067.58885583072</v>
       </c>
       <c r="H32" s="121"/>
     </row>
@@ -15828,19 +15859,19 @@
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>197068.80993074423</v>
       </c>
       <c r="D33" s="139">
         <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
-        <v>0</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E33" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.36769792467221413</v>
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>72461.792429157678</v>
       </c>
       <c r="H33" s="121"/>
     </row>
@@ -15850,19 +15881,19 @@
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>205446.26743025903</v>
       </c>
       <c r="D34" s="139">
         <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
-        <v>0</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E34" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.34046104136316119</v>
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>69946.450153480502</v>
       </c>
       <c r="H34" s="121"/>
     </row>
@@ -15872,19 +15903,19 @@
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>214179.85330026961</v>
       </c>
       <c r="D35" s="139">
         <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
-        <v>0</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E35" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.31524170496588994</v>
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>67518.422123721175</v>
       </c>
       <c r="H35" s="121"/>
     </row>
@@ -15894,19 +15925,19 @@
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>223284.70667055121</v>
       </c>
       <c r="D36" s="139">
         <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
-        <v>0</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E36" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.29189046756100923</v>
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>65174.677429289986</v>
       </c>
       <c r="H36" s="121"/>
     </row>
@@ -15916,19 +15947,19 @@
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>232776.61024007871</v>
       </c>
       <c r="D37" s="139">
         <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
-        <v>0</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E37" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.27026895144537894</v>
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62912.290370595729</v>
       </c>
       <c r="H37" s="121"/>
     </row>
@@ -15938,19 +15969,19 @@
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>242672.01763535704</v>
       </c>
       <c r="D38" s="139">
         <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
-        <v>0</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E38" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.25024902911609154</v>
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>60728.436806891143</v>
       </c>
       <c r="H38" s="121"/>
     </row>
@@ -15960,19 +15991,19 @@
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>252988.08193176272</v>
       </c>
       <c r="D39" s="139">
         <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
-        <v>0</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E39" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.23171206399638106</v>
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>58620.390630894297</v>
       </c>
       <c r="H39" s="121"/>
     </row>
@@ -15982,19 +16013,19 @@
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>263742.68538733711</v>
       </c>
       <c r="D40" s="139">
         <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
-        <v>0</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E40" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.21454820740405653</v>
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>56585.520365785233</v>
       </c>
       <c r="H40" s="121"/>
     </row>
@@ -16004,19 +16035,19 @@
       </c>
       <c r="C41" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>274954.47044057207</v>
       </c>
       <c r="D41" s="139">
         <f>IF($C$17&lt;B41,0,DCF!$C$16)</f>
-        <v>0</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E41" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.19865574759634863</v>
       </c>
       <c r="F41" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>54621.285880329982</v>
       </c>
       <c r="H41" s="121"/>
     </row>
@@ -16026,19 +16057,19 @@
       </c>
       <c r="C42" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>286642.87202592177</v>
       </c>
       <c r="D42" s="139">
         <f>IF($C$17&lt;B42,0,DCF!$C$16)</f>
-        <v>0</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E42" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.18394050703365611</v>
       </c>
       <c r="F42" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>52725.235218031448</v>
       </c>
       <c r="H42" s="121"/>
     </row>
@@ -16048,19 +16079,19 @@
       </c>
       <c r="C43" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>298828.15126305691</v>
       </c>
       <c r="D43" s="139">
         <f>IF($C$17&lt;B43,0,DCF!$C$16)</f>
-        <v>0</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E43" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.17031528429042234</v>
       </c>
       <c r="F43" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>50895.001536348864</v>
       </c>
       <c r="H43" s="121"/>
     </row>
@@ -16070,19 +16101,19 @@
       </c>
       <c r="C44" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>311531.43057825958</v>
       </c>
       <c r="D44" s="139">
         <f>IF($C$17&lt;B44,0,DCF!$C$16)</f>
-        <v>0</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E44" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1576993373059466</v>
       </c>
       <c r="F44" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>49128.300152165044</v>
       </c>
       <c r="H44" s="121"/>
     </row>
@@ -16092,19 +16123,19 @@
       </c>
       <c r="C45" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>324774.73031884048</v>
       </c>
       <c r="D45" s="139">
         <f>IF($C$17&lt;B45,0,DCF!$C$16)</f>
-        <v>0</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E45" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1460179049129135</v>
       </c>
       <c r="F45" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>47422.925689813572</v>
       </c>
       <c r="H45" s="121"/>
     </row>
@@ -16114,19 +16145,19 @@
       </c>
       <c r="C46" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>338581.00692404574</v>
       </c>
       <c r="D46" s="139">
         <f>IF($C$17&lt;B46,0,DCF!$C$16)</f>
-        <v>0</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E46" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.13520176380825324</v>
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>45776.74932810539</v>
       </c>
       <c r="H46" s="121"/>
     </row>
@@ -16136,19 +16167,19 @@
       </c>
       <c r="C47" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>352974.1927186214</v>
       </c>
       <c r="D47" s="139">
         <f>IF($C$17&lt;B47,0,DCF!$C$16)</f>
-        <v>0</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E47" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.12518681834097523</v>
       </c>
       <c r="F47" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>44187.716142918434</v>
       </c>
       <c r="H47" s="121"/>
     </row>
@@ -16158,19 +16189,19 @@
       </c>
       <c r="C48" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>367979.23739801534</v>
       </c>
       <c r="D48" s="139">
         <f>IF($C$17&lt;B48,0,DCF!$C$16)</f>
-        <v>0</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E48" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.11591372068608817</v>
       </c>
       <c r="F48" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>42653.842542033279</v>
       </c>
       <c r="H48" s="121"/>
     </row>
@@ -16180,19 +16211,19 @@
       </c>
       <c r="C49" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>383622.15127712738</v>
       </c>
       <c r="D49" s="139">
         <f>IF($C$17&lt;B49,0,DCF!$C$16)</f>
-        <v>0</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E49" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.10732751915378534</v>
       </c>
       <c r="F49" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>41173.213789012225</v>
       </c>
       <c r="H49" s="121"/>
     </row>
@@ -16202,19 +16233,19 @@
       </c>
       <c r="C50" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>399930.05037757859</v>
       </c>
       <c r="D50" s="139">
         <f>IF($C$17&lt;B50,0,DCF!$C$16)</f>
-        <v>0</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E50" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9.9377332549801231E-2</v>
       </c>
       <c r="F50" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>39743.981613031385</v>
       </c>
       <c r="H50" s="121"/>
     </row>
@@ -16224,7 +16255,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>-1873024.5334744046</v>
+        <v>1494732.8187061104</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16232,11 +16263,11 @@
       </c>
       <c r="E51" s="125">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.46319348808468425</v>
+        <v>9.9377332549801231E-2</v>
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>-867572.76692819793</v>
+        <v>148542.56039765888</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -16247,7 +16278,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>-2076884.6114418618</v>
+        <v>2232985.7332331189</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -16268,7 +16299,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>-2076884.6114418618</v>
+        <v>2232985.7332331189</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16276,19 +16307,19 @@
       </c>
       <c r="C55" s="132">
         <f>C77</f>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D55" s="132">
         <f>C76</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="E55" s="132">
         <f>C75</f>
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="F55" s="132">
         <f>C74</f>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H55" s="121"/>
     </row>
@@ -16298,19 +16329,19 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>-1789670.8449357809</v>
+        <v>1433782.2800642184</v>
       </c>
       <c r="C56" s="124">
-        <v>-1789670.8449357809</v>
+        <v>1480043.6018848091</v>
       </c>
       <c r="D56" s="124">
-        <v>-1847414.9948403216</v>
+        <v>1527690.4301062953</v>
       </c>
       <c r="E56" s="124">
-        <v>-1906888.5568359671</v>
+        <v>1576783.5652253886</v>
       </c>
       <c r="F56" s="124">
-        <v>-1968167.423112093</v>
+        <v>1627385.6902834533</v>
       </c>
       <c r="H56" s="121"/>
     </row>
@@ -16319,19 +16350,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>-1789670.8449357804</v>
+        <v>1433782.2800642182</v>
       </c>
       <c r="C57" s="124">
-        <v>-1789670.8449357804</v>
+        <v>1526347.5230723554</v>
       </c>
       <c r="D57" s="124">
-        <v>-1905212.3179819107</v>
+        <v>1628190.3097296776</v>
       </c>
       <c r="E57" s="124">
-        <v>-2032334.1750322436</v>
+        <v>1740420.958714019</v>
       </c>
       <c r="F57" s="124">
-        <v>-2172422.334293426</v>
+        <v>1864273.9287448889</v>
       </c>
       <c r="H57" s="121"/>
     </row>
@@ -16340,19 +16371,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>-1789670.8449357804</v>
+        <v>1433782.280064218</v>
       </c>
       <c r="C58" s="124">
-        <v>-1789670.8449357804</v>
+        <v>1583661.4644162063</v>
       </c>
       <c r="D58" s="124">
-        <v>-1976752.5310656261</v>
+        <v>1759204.6477251006</v>
       </c>
       <c r="E58" s="124">
-        <v>-2195868.4467547736</v>
+        <v>1965510.5067752679</v>
       </c>
       <c r="F58" s="124">
-        <v>-2453382.8450112357</v>
+        <v>2208685.7442357745</v>
       </c>
       <c r="H58" s="121"/>
     </row>
@@ -16361,19 +16392,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>-1789670.8449357804</v>
+        <v>1433782.2800642177</v>
       </c>
       <c r="C59" s="124">
-        <v>-1789670.8449357804</v>
+        <v>1642055.1793496069</v>
       </c>
       <c r="D59" s="124">
-        <v>-2049640.5354696955</v>
+        <v>1900218.7932793819</v>
       </c>
       <c r="E59" s="124">
-        <v>-2371884.6442842372</v>
+        <v>2222276.49861127</v>
       </c>
       <c r="F59" s="124">
-        <v>-2773882.4187256834</v>
+        <v>2626276.2995378673</v>
       </c>
       <c r="H59" s="121"/>
     </row>
@@ -16382,19 +16413,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>-1789670.8449357799</v>
+        <v>1433782.2800642177</v>
       </c>
       <c r="C60" s="124">
-        <v>-1789670.8449357799</v>
+        <v>1696364.5745054719</v>
       </c>
       <c r="D60" s="124">
-        <v>-2117430.4241215452</v>
+        <v>2039122.5238502626</v>
       </c>
       <c r="E60" s="124">
-        <v>-2545266.586795331</v>
+        <v>2491359.4511116408</v>
       </c>
       <c r="F60" s="124">
-        <v>-3109756.227221617</v>
+        <v>3093671.0755355731</v>
       </c>
       <c r="H60" s="121"/>
     </row>
@@ -16403,19 +16434,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>-1789670.8449357799</v>
+        <v>1433782.2800642182</v>
       </c>
       <c r="C61" s="124">
-        <v>-1789670.8449357799</v>
+        <v>1744273.0159140313</v>
       </c>
       <c r="D61" s="124">
-        <v>-2177230.5360404709</v>
+        <v>2169207.0985259619</v>
       </c>
       <c r="E61" s="124">
-        <v>-2707640.3125067013</v>
+        <v>2760408.2084358027</v>
       </c>
       <c r="F61" s="124">
-        <v>-3445587.3527309163</v>
+        <v>3594961.7672800743</v>
       </c>
       <c r="H61" s="121"/>
     </row>
@@ -16443,19 +16474,19 @@
       </c>
       <c r="C64" s="133">
         <f>C55</f>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D64" s="133">
         <f>D55</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="E64" s="133">
         <f>E55</f>
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="F64" s="133">
         <f>F55</f>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="H64" s="121"/>
     </row>
@@ -16465,23 +16496,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>-118.69228650791112</v>
+        <v>-285.78567749520096</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>-118.69228650791112</v>
+        <v>-285.78567749520096</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>-118.69228650791112</v>
+        <v>-285.78567749520096</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>-118.69228650791112</v>
+        <v>-285.78567749520096</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>-118.69228650791112</v>
+        <v>-285.78567749520096</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16492,23 +16523,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>-118.69228650791111</v>
+        <v>-285.78567749520096</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
+        <v>-283.55882524358969</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>-121.47188045749577</v>
+        <v>-281.26527973880218</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>-124.33472203290434</v>
+        <v>-278.90211426543806</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>-127.28446440888702</v>
+        <v>-276.4663114892254</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16519,23 +16550,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
+        <v>-285.78567749520101</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
+        <v>-281.32992241295295</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>-124.25403397386283</v>
+        <v>-276.42758002728266</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>-130.37321912597261</v>
+        <v>-271.02520362394938</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>-137.11655504025211</v>
+        <v>-265.06337083733803</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16546,23 +16577,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
+        <v>-285.78567749520101</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
+        <v>-278.57103714319709</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>-127.69772036925049</v>
+        <v>-270.12102495974887</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>-138.24516585964389</v>
+        <v>-260.1902091363678</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>-150.64097503698704</v>
+        <v>-248.48463515438991</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16573,23 +16604,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
+        <v>-285.78567749520101</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
+        <v>-275.76017548896937</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>-131.20628455062251</v>
+        <v>-263.33311542369211</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>-146.71794723213949</v>
+        <v>-247.83042552978083</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>-166.06866212587562</v>
+        <v>-228.38334034201091</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16600,23 +16631,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
+        <v>-285.78567749520101</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
+        <v>-273.14591817579742</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>-134.46944392955865</v>
+        <v>-256.64679361087087</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>-155.06392512198221</v>
+        <v>-234.87774810803597</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>-182.2364091177804</v>
+        <v>-205.88465097558353</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16626,23 +16657,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
+        <v>-285.78567749520101</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
+        <v>-270.83977956100432</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>-137.34800443394067</v>
+        <v>-250.38499397747751</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>-162.88000737975133</v>
+        <v>-221.92671671805448</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>-198.40210150551155</v>
+        <v>-181.75433515901051</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16669,15 +16700,15 @@
       </c>
       <c r="C74" s="143">
         <f>Scenarios!C56</f>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="D74" s="146">
         <f>Scenarios!C55</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>-150.64097503698704</v>
+        <v>-181.75433515901051</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16691,15 +16722,15 @@
       </c>
       <c r="C75" s="143">
         <f>Scenarios!C38</f>
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="D75" s="146">
         <f>Scenarios!C37</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>-130.37321912597261</v>
+        <v>-221.92671671805448</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16714,15 +16745,15 @@
       </c>
       <c r="C76" s="143">
         <f>Scenarios!C26</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D76" s="146">
         <f>Scenarios!C25</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>-124.25403397386283</v>
+        <v>-250.38499397747751</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16737,15 +16768,15 @@
       </c>
       <c r="C77" s="143">
         <f>Scenarios!C32</f>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D77" s="146">
         <f>Scenarios!C31</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>-118.69228650791111</v>
+        <v>-270.83977956100432</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16764,11 +16795,11 @@
       </c>
       <c r="D78" s="146">
         <f>Scenarios!C49</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>-118.69228650791111</v>
+        <v>-285.78567749520101</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16784,7 +16815,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16839,7 +16870,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H94"/>
+  <dimension ref="A2:H89"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -16851,7 +16882,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>55</v>
+        <v>453</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -16863,7 +16894,7 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>164</v>
+        <v>452</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
@@ -16876,22 +16907,22 @@
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>129</v>
+        <v>450</v>
       </c>
       <c r="C4" s="110">
-        <f>Normalized_FCF!C19</f>
-        <v>-143173.66759486249</v>
+        <f>Normalized_FCF!C91</f>
+        <v>22020.769943020001</v>
       </c>
       <c r="D4" t="str">
-        <f>Reporting_currency</f>
+        <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C86</f>
-        <v>0</v>
+        <f>Thesis!E22</f>
+        <v>0.02</v>
       </c>
       <c r="H4" s="121"/>
     </row>
@@ -16900,7 +16931,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C80</f>
+        <f>Equity_Cost</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -16908,1454 +16939,1376 @@
     </row>
     <row r="6" spans="2:8" ht="13.15" customHeight="1">
       <c r="B6" s="150" t="s">
-        <v>229</v>
+        <v>451</v>
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>-1789670.8449357811</v>
+        <v>275259.62428774999</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356" t="s">
-        <v>250</v>
-      </c>
-      <c r="F6" s="356"/>
+      <c r="E6" s="357"/>
+      <c r="F6" s="357"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8">
-      <c r="B7" s="149" t="s">
-        <v>225</v>
-      </c>
-      <c r="C7" s="226">
-        <f>BS!G31</f>
-        <v>9516669</v>
+    <row r="7" spans="2:8" ht="13.15">
+      <c r="B7" s="150" t="s">
+        <v>454</v>
+      </c>
+      <c r="C7" s="112">
+        <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
+        <v>13.25</v>
       </c>
       <c r="D7" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
-      <c r="H7" s="121"/>
-    </row>
-    <row r="8" spans="2:8">
-      <c r="B8" s="149" t="s">
-        <v>226</v>
-      </c>
-      <c r="C8" s="201">
-        <f>BS!D66</f>
-        <v>6694703.2400284903</v>
-      </c>
-      <c r="D8" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
-      <c r="H8" s="121"/>
-    </row>
-    <row r="9" spans="2:8">
-      <c r="B9" s="227" t="s">
-        <v>191</v>
-      </c>
-      <c r="C9" s="229">
-        <f>BS!H42</f>
-        <v>2145886.1</v>
-      </c>
-      <c r="D9" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
-      <c r="H9" s="121"/>
-    </row>
-    <row r="10" spans="2:8" ht="13.15">
-      <c r="B10" s="150" t="s">
-        <v>228</v>
-      </c>
-      <c r="C10" s="232">
-        <f>C6-C7+C8+C9</f>
-        <v>-2465750.50490729</v>
-      </c>
-      <c r="D10" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-      <c r="H10" s="121"/>
-    </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1">
-      <c r="B11" s="230" t="s">
-        <v>167</v>
-      </c>
-      <c r="C11" s="231">
-        <f>Exchange_Rate</f>
-        <v>1</v>
-      </c>
-      <c r="D11" t="str">
-        <f>Thesis!C15</f>
-        <v>CNY</v>
-      </c>
-      <c r="H11" s="121"/>
-    </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1">
-      <c r="B12" s="150" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="112">
-        <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>-118.69228650791112</v>
-      </c>
-      <c r="D12" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
+      <c r="H7" s="121"/>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="H8" s="121"/>
+    </row>
+    <row r="9" spans="2:8" ht="13.9">
+      <c r="B9" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="H9" s="121"/>
+    </row>
+    <row r="10" spans="2:8" ht="13.15">
+      <c r="B10" s="120" t="s">
+        <v>136</v>
+      </c>
+      <c r="H10" s="121"/>
+    </row>
+    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B11" s="153" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="162">
+        <f>Scenarios!C65</f>
+        <v>4.2510316586672814E-2</v>
+      </c>
+      <c r="H11" s="121"/>
+    </row>
+    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B12" s="119" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="163">
+        <f>Scenarios!C64</f>
+        <v>30</v>
+      </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8">
-      <c r="H13" s="121"/>
-    </row>
-    <row r="14" spans="2:8" ht="13.9">
-      <c r="B14" s="36" t="s">
-        <v>230</v>
-      </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="H14" s="121"/>
-    </row>
-    <row r="15" spans="2:8" ht="13.15">
-      <c r="B15" s="120" t="s">
-        <v>136</v>
-      </c>
-      <c r="H15" s="121"/>
-    </row>
-    <row r="16" spans="2:8" ht="13.35" customHeight="1">
-      <c r="B16" s="153" t="s">
-        <v>134</v>
-      </c>
-      <c r="C16" s="162">
-        <f>Scenarios!C65</f>
-        <v>4.6574870890079501E-2</v>
-      </c>
-      <c r="H16" s="121"/>
-    </row>
-    <row r="17" spans="2:8" ht="13.35" customHeight="1">
-      <c r="B17" s="119" t="s">
-        <v>135</v>
-      </c>
-      <c r="C17" s="163">
-        <f>Scenarios!C64</f>
-        <v>10</v>
-      </c>
-      <c r="H17" s="121"/>
-    </row>
-    <row r="18" spans="2:8" ht="13.35" customHeight="1">
-      <c r="B18" s="154" t="s">
+    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B13" s="154" t="s">
         <v>107</v>
       </c>
-      <c r="C18" s="141">
-        <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>-132.51771555894882</v>
-      </c>
-      <c r="D18" t="str">
+      <c r="C13" s="141">
+        <f>F47/Common_Shares*scaling_factor</f>
+        <v>21.74944849239106</v>
+      </c>
+      <c r="D13" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
+      <c r="H13" s="121"/>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="H14" s="121"/>
+    </row>
+    <row r="15" spans="2:8" ht="13.15">
+      <c r="B15" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="129" t="s">
+        <v>456</v>
+      </c>
+      <c r="D15" s="129" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="130" t="s">
+        <v>455</v>
+      </c>
+      <c r="H15" s="121"/>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" s="123">
+        <v>1</v>
+      </c>
+      <c r="C16" s="124">
+        <f>C4*(1+D16)</f>
+        <v>22956.879844780073</v>
+      </c>
+      <c r="D16" s="139">
+        <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
+      </c>
+      <c r="E16" s="125">
+        <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
+        <v>0.92592592592592582</v>
+      </c>
+      <c r="F16" s="126">
+        <f t="shared" ref="F16:F46" si="1">C16*E16</f>
+        <v>21256.370226648214</v>
+      </c>
+      <c r="H16" s="121"/>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="123">
+        <v>2</v>
+      </c>
+      <c r="C17" s="124">
+        <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
+        <v>23932.784074823885</v>
+      </c>
+      <c r="D17" s="139">
+        <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
+      </c>
+      <c r="E17" s="125">
+        <f t="shared" si="0"/>
+        <v>0.85733882030178321</v>
+      </c>
+      <c r="F17" s="126">
+        <f t="shared" si="1"/>
+        <v>20518.504865246814</v>
+      </c>
+      <c r="H17" s="121"/>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="123">
+        <v>3</v>
+      </c>
+      <c r="C18" s="124">
+        <f t="shared" si="2"/>
+        <v>24950.174302645133</v>
+      </c>
+      <c r="D18" s="139">
+        <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
+      </c>
+      <c r="E18" s="125">
+        <f t="shared" si="0"/>
+        <v>0.79383224102016958</v>
+      </c>
+      <c r="F18" s="126">
+        <f t="shared" si="1"/>
+        <v>19806.252780512634</v>
+      </c>
       <c r="H18" s="121"/>
     </row>
     <row r="19" spans="2:8">
+      <c r="B19" s="123">
+        <v>4</v>
+      </c>
+      <c r="C19" s="124">
+        <f t="shared" si="2"/>
+        <v>26010.814111143245</v>
+      </c>
+      <c r="D19" s="139">
+        <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
+      </c>
+      <c r="E19" s="125">
+        <f t="shared" si="0"/>
+        <v>0.73502985279645328</v>
+      </c>
+      <c r="F19" s="126">
+        <f t="shared" si="1"/>
+        <v>19118.724867229528</v>
+      </c>
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15">
-      <c r="B20" s="129" t="s">
-        <v>108</v>
-      </c>
-      <c r="C20" s="129" t="s">
-        <v>109</v>
-      </c>
-      <c r="D20" s="129" t="s">
-        <v>119</v>
-      </c>
-      <c r="E20" s="129" t="s">
-        <v>110</v>
-      </c>
-      <c r="F20" s="130" t="s">
-        <v>111</v>
+    <row r="20" spans="2:8">
+      <c r="B20" s="123">
+        <v>5</v>
+      </c>
+      <c r="C20" s="124">
+        <f t="shared" si="2"/>
+        <v>27116.542053685043</v>
+      </c>
+      <c r="D20" s="139">
+        <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
+      </c>
+      <c r="E20" s="125">
+        <f t="shared" si="0"/>
+        <v>0.68058319703375303</v>
+      </c>
+      <c r="F20" s="126">
+        <f t="shared" si="1"/>
+        <v>18455.062883397179</v>
       </c>
       <c r="H20" s="121"/>
     </row>
     <row r="21" spans="2:8">
       <c r="B21" s="123">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C21" s="124">
-        <f>C4*(1+D21)</f>
-        <v>-149841.96267795237</v>
+        <f t="shared" si="2"/>
+        <v>28269.274841123024</v>
       </c>
       <c r="D21" s="139">
-        <f>IF($C$17&lt;B21,0,DDM!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E21" s="125">
-        <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.92592592592592582</v>
+        <f t="shared" si="0"/>
+        <v>0.63016962688310452</v>
       </c>
       <c r="F21" s="126">
-        <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>-138742.55803514106</v>
+        <f t="shared" si="1"/>
+        <v>17814.438378886429</v>
       </c>
       <c r="H21" s="121"/>
     </row>
     <row r="22" spans="2:8">
       <c r="B22" s="123">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C22" s="124">
-        <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>-156820.8327435941</v>
+        <f t="shared" si="2"/>
+        <v>29471.01066429483</v>
       </c>
       <c r="D22" s="139">
-        <f>IF($C$17&lt;B22,0,DDM!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.58349039526213387</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>-134448.58774313622</v>
+        <v>17196.051661283953</v>
       </c>
       <c r="H22" s="121"/>
     </row>
     <row r="23" spans="2:8">
       <c r="B23" s="123">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>-164124.74278150176</v>
+        <v>30723.832657763218</v>
       </c>
       <c r="D23" s="139">
-        <f>IF($C$17&lt;B23,0,DDM!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.54026888450197574</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>-130287.51236909845</v>
+        <v>16599.130797635105</v>
       </c>
       <c r="H23" s="121"/>
     </row>
     <row r="24" spans="2:8">
       <c r="B24" s="123">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>-171768.83148641774</v>
+        <v>32029.912510800688</v>
       </c>
       <c r="D24" s="139">
-        <f>IF($C$17&lt;B24,0,DDM!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.50024896713145905</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>-126255.21892248042</v>
+        <v>16022.930650839042</v>
       </c>
       <c r="H24" s="121"/>
     </row>
     <row r="25" spans="2:8">
       <c r="B25" s="123">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>-179768.94263583748</v>
+        <v>33391.51423187826</v>
       </c>
       <c r="D25" s="139">
-        <f>IF($C$17&lt;B25,0,DDM!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.46319348808468425</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>-122347.72170647563</v>
+        <v>15466.731949493067</v>
       </c>
       <c r="H25" s="121"/>
     </row>
     <row r="26" spans="2:8">
       <c r="B26" s="123">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>-188141.65792914771</v>
+        <v>34810.9980731838</v>
       </c>
       <c r="D26" s="139">
-        <f>IF($C$17&lt;B26,0,DDM!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.42888285933767062</v>
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>-118561.1583783797</v>
+        <v>14929.840390025211</v>
       </c>
       <c r="H26" s="121"/>
     </row>
     <row r="27" spans="2:8">
       <c r="B27" s="123">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>-196904.33135624332</v>
+        <v>36290.824621972904</v>
       </c>
       <c r="D27" s="139">
-        <f>IF($C$17&lt;B27,0,DDM!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.39711375864599124</v>
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>-114891.7861318806</v>
+        <v>14411.585769994144</v>
       </c>
       <c r="H27" s="121"/>
     </row>
     <row r="28" spans="2:8">
       <c r="B28" s="123">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>-206075.12516685776</v>
+        <v>37833.559065844398</v>
       </c>
       <c r="D28" s="139">
-        <f>IF($C$17&lt;B28,0,DDM!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.36769792467221413</v>
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>-111335.97799750327</v>
+        <v>13911.321151474618</v>
       </c>
       <c r="H28" s="121"/>
     </row>
     <row r="29" spans="2:8">
       <c r="B29" s="123">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>-215673.04751516116</v>
+        <v>39441.87563933403</v>
       </c>
       <c r="D29" s="139">
-        <f>IF($C$17&lt;B29,0,DDM!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.34046104136316119</v>
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>-107890.21925755346</v>
+        <v>13428.422053483962</v>
       </c>
       <c r="H29" s="121"/>
     </row>
     <row r="30" spans="2:8">
       <c r="B30" s="123">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>-225717.99185764979</v>
+        <v>41118.562259534301</v>
       </c>
       <c r="D30" s="139">
-        <f>IF($C$17&lt;B30,0,DDM!$C$16)</f>
-        <v>4.6574870890079501E-2</v>
+        <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.31524170496588994</v>
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>-104551.10397201516</v>
+        <v>12962.285672441689</v>
       </c>
       <c r="H30" s="121"/>
     </row>
     <row r="31" spans="2:8">
       <c r="B31" s="123">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C31" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>42866.525358775922</v>
       </c>
       <c r="D31" s="139">
-        <f>IF($C$17&lt;B31,0,DDM!$C$16)</f>
-        <v>0</v>
+        <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E31" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.29189046756100923</v>
       </c>
       <c r="F31" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12512.330129688962</v>
       </c>
       <c r="H31" s="121"/>
     </row>
     <row r="32" spans="2:8">
       <c r="B32" s="123">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C32" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>44688.794922748122</v>
       </c>
       <c r="D32" s="139">
-        <f>IF($C$17&lt;B32,0,DDM!$C$16)</f>
-        <v>0</v>
+        <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E32" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.27026895144537894</v>
       </c>
       <c r="F32" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>12077.99374512871</v>
       </c>
       <c r="H32" s="121"/>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" s="123">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C33" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>46588.529742791055</v>
       </c>
       <c r="D33" s="139">
-        <f>IF($C$17&lt;B33,0,DDM!$C$16)</f>
-        <v>0</v>
+        <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E33" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.25024902911609154</v>
       </c>
       <c r="F33" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11658.734336079615</v>
       </c>
       <c r="H33" s="121"/>
     </row>
     <row r="34" spans="2:8">
       <c r="B34" s="123">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C34" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>48569.022891464723</v>
       </c>
       <c r="D34" s="139">
-        <f>IF($C$17&lt;B34,0,DDM!$C$16)</f>
-        <v>0</v>
+        <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E34" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.23171206399638106</v>
       </c>
       <c r="F34" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11254.028540468771</v>
       </c>
       <c r="H34" s="121"/>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" s="123">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C35" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>50633.707430886257</v>
       </c>
       <c r="D35" s="139">
-        <f>IF($C$17&lt;B35,0,DDM!$C$16)</f>
-        <v>0</v>
+        <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E35" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.21454820740405653</v>
       </c>
       <c r="F35" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10863.371163518103</v>
       </c>
       <c r="H35" s="121"/>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" s="123">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C36" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>52786.162363730204</v>
       </c>
       <c r="D36" s="139">
-        <f>IF($C$17&lt;B36,0,DDM!$C$16)</f>
-        <v>0</v>
+        <f>IF($C$12&lt;B36,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E36" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.19865574759634863</v>
       </c>
       <c r="F36" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10486.274547109066</v>
       </c>
       <c r="H36" s="121"/>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" s="123">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C37" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>55030.11883720789</v>
       </c>
       <c r="D37" s="139">
-        <f>IF($C$17&lt;B37,0,DDM!$C$16)</f>
-        <v>0</v>
+        <f>IF($C$12&lt;B37,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E37" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.18394050703365611</v>
       </c>
       <c r="F37" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10122.267961038369</v>
       </c>
       <c r="H37" s="121"/>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" s="123">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C38" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>57369.466610779826</v>
       </c>
       <c r="D38" s="139">
-        <f>IF($C$17&lt;B38,0,DDM!$C$16)</f>
-        <v>0</v>
+        <f>IF($C$12&lt;B38,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E38" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.17031528429042234</v>
       </c>
       <c r="F38" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9770.8970154048584</v>
       </c>
       <c r="H38" s="121"/>
     </row>
     <row r="39" spans="2:8">
       <c r="B39" s="123">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C39" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>59808.260798812633</v>
       </c>
       <c r="D39" s="139">
-        <f>IF($C$17&lt;B39,0,DDM!$C$16)</f>
-        <v>0</v>
+        <f>IF($C$12&lt;B39,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E39" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1576993373059466</v>
       </c>
       <c r="F39" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9431.7230933939773</v>
       </c>
       <c r="H39" s="121"/>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" s="123">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C40" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>62350.728899868453</v>
       </c>
       <c r="D40" s="139">
-        <f>IF($C$17&lt;B40,0,DDM!$C$16)</f>
-        <v>0</v>
+        <f>IF($C$12&lt;B40,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E40" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1460179049129135</v>
       </c>
       <c r="F40" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9104.3228037518402</v>
       </c>
       <c r="H40" s="121"/>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" s="123">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C41" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>65001.278124811681</v>
       </c>
       <c r="D41" s="139">
-        <f>IF($C$17&lt;B41,0,DDM!$C$16)</f>
-        <v>0</v>
+        <f>IF($C$12&lt;B41,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E41" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.13520176380825324</v>
       </c>
       <c r="F41" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8788.2874522653674</v>
       </c>
       <c r="H41" s="121"/>
     </row>
     <row r="42" spans="2:8">
       <c r="B42" s="123">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C42" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>67764.503036435795</v>
       </c>
       <c r="D42" s="139">
-        <f>IF($C$17&lt;B42,0,DDM!$C$16)</f>
-        <v>0</v>
+        <f>IF($C$12&lt;B42,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E42" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.12518681834097523</v>
       </c>
       <c r="F42" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8483.2225315887517</v>
       </c>
       <c r="H42" s="121"/>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" s="123">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C43" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>70645.193513853243</v>
       </c>
       <c r="D43" s="139">
-        <f>IF($C$17&lt;B43,0,DDM!$C$16)</f>
-        <v>0</v>
+        <f>IF($C$12&lt;B43,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E43" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.11591372068608817</v>
       </c>
       <c r="F43" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8188.7472287794326</v>
       </c>
       <c r="H43" s="121"/>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" s="123">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C44" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>73648.343055453908</v>
       </c>
       <c r="D44" s="139">
-        <f>IF($C$17&lt;B44,0,DDM!$C$16)</f>
-        <v>0</v>
+        <f>IF($C$12&lt;B44,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E44" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.10732751915378534</v>
       </c>
       <c r="F44" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7904.493949928783</v>
       </c>
       <c r="H44" s="121"/>
     </row>
     <row r="45" spans="2:8">
       <c r="B45" s="123">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C45" s="124">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>76779.157434825145</v>
       </c>
       <c r="D45" s="139">
-        <f>IF($C$17&lt;B45,0,DDM!$C$16)</f>
-        <v>0</v>
+        <f>IF($C$12&lt;B45,0,DDM!$C$11)</f>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="E45" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9.9377332549801231E-2</v>
       </c>
       <c r="F45" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7630.1078612941619</v>
       </c>
       <c r="H45" s="121"/>
     </row>
     <row r="46" spans="2:8">
-      <c r="B46" s="123">
-        <v>26</v>
+      <c r="B46" s="127" t="s">
+        <v>132</v>
       </c>
       <c r="C46" s="124">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D46" s="139">
-        <f>IF($C$17&lt;B46,0,DDM!$C$16)</f>
+        <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
+        <v>519790.12802138977</v>
+      </c>
+      <c r="D46" s="140">
+        <f>Terminal_Growth</f>
         <v>0</v>
       </c>
       <c r="E46" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>1/(1+Equity_Cost)^C12</f>
+        <v>9.9377332549801231E-2</v>
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>51655.356408485408</v>
       </c>
       <c r="H46" s="121"/>
     </row>
     <row r="47" spans="2:8">
-      <c r="B47" s="123">
-        <v>27</v>
-      </c>
-      <c r="C47" s="124">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D47" s="139">
-        <f>IF($C$17&lt;B47,0,DDM!$C$16)</f>
-        <v>0</v>
-      </c>
-      <c r="E47" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F47" s="126">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="C47" s="115"/>
+      <c r="E47" s="128" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" s="138">
+        <f>SUM(F16:F46)</f>
+        <v>451829.81286651577</v>
       </c>
       <c r="H47" s="121"/>
     </row>
     <row r="48" spans="2:8">
-      <c r="B48" s="123">
-        <v>28</v>
-      </c>
-      <c r="C48" s="124">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D48" s="139">
-        <f>IF($C$17&lt;B48,0,DDM!$C$16)</f>
-        <v>0</v>
-      </c>
-      <c r="E48" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F48" s="126">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="C48" s="115"/>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8">
-      <c r="B49" s="123">
-        <v>29</v>
-      </c>
-      <c r="C49" s="124">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D49" s="139">
-        <f>IF($C$17&lt;B49,0,DDM!$C$16)</f>
-        <v>0</v>
-      </c>
-      <c r="E49" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F49" s="126">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+    <row r="49" spans="1:8" ht="13.15">
+      <c r="B49" s="120" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" s="137"/>
+      <c r="D49" s="137"/>
+      <c r="E49" s="118"/>
+      <c r="F49" s="118"/>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8">
-      <c r="B50" s="123">
+    <row r="50" spans="1:8" ht="13.15">
+      <c r="A50" s="134">
+        <f>F47</f>
+        <v>451829.81286651577</v>
+      </c>
+      <c r="B50" s="132">
+        <f>C73</f>
+        <v>0</v>
+      </c>
+      <c r="C50" s="132">
+        <f>C72</f>
+        <v>0.02</v>
+      </c>
+      <c r="D50" s="132">
+        <f>C71</f>
+        <v>0.04</v>
+      </c>
+      <c r="E50" s="132">
+        <f>C70</f>
+        <v>0.06</v>
+      </c>
+      <c r="F50" s="132">
+        <f>C69</f>
+        <v>0.08</v>
+      </c>
+      <c r="H50" s="121"/>
+    </row>
+    <row r="51" spans="1:8" ht="13.15">
+      <c r="A51" s="144">
+        <v>5</v>
+      </c>
+      <c r="B51" s="124">
+        <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
+        <v>294757.8175345526</v>
+      </c>
+      <c r="C51" s="124">
+        <v>304029.09778932447</v>
+      </c>
+      <c r="D51" s="124">
+        <v>313566.36959432089</v>
+      </c>
+      <c r="E51" s="124">
+        <v>323381.30551804398</v>
+      </c>
+      <c r="F51" s="124">
+        <v>333485.93954267877</v>
+      </c>
+      <c r="H51" s="121"/>
+    </row>
+    <row r="52" spans="1:8" ht="13.15">
+      <c r="A52" s="144">
+        <v>10</v>
+      </c>
+      <c r="B52" s="124">
+        <v>303181.07679074019</v>
+      </c>
+      <c r="C52" s="124">
+        <v>321510.31690939749</v>
+      </c>
+      <c r="D52" s="124">
+        <v>341620.67346023262</v>
+      </c>
+      <c r="E52" s="124">
+        <v>363725.30705092638</v>
+      </c>
+      <c r="F52" s="124">
+        <v>388061.21087636997</v>
+      </c>
+      <c r="H52" s="121"/>
+    </row>
+    <row r="53" spans="1:8" ht="13.15">
+      <c r="A53" s="144">
+        <v>15</v>
+      </c>
+      <c r="B53" s="124">
+        <v>305271.76595888828</v>
+      </c>
+      <c r="C53" s="124">
+        <v>334646.03435178101</v>
+      </c>
+      <c r="D53" s="124">
+        <v>368947.31489207054</v>
+      </c>
+      <c r="E53" s="124">
+        <v>409154.45902432024</v>
+      </c>
+      <c r="F53" s="124">
+        <v>456439.84048036946</v>
+      </c>
+      <c r="H53" s="121"/>
+    </row>
+    <row r="54" spans="1:8" ht="13.15">
+      <c r="A54" s="145">
+        <v>20</v>
+      </c>
+      <c r="B54" s="124">
+        <v>303957.95673586661</v>
+      </c>
+      <c r="C54" s="124">
+        <v>344516.45995201886</v>
+      </c>
+      <c r="D54" s="124">
+        <v>394653.05571360677</v>
+      </c>
+      <c r="E54" s="124">
+        <v>457056.13282183616</v>
+      </c>
+      <c r="F54" s="124">
+        <v>535190.57358294923</v>
+      </c>
+      <c r="H54" s="121"/>
+    </row>
+    <row r="55" spans="1:8" ht="13.15">
+      <c r="A55" s="145">
+        <v>25</v>
+      </c>
+      <c r="B55" s="124">
+        <v>301007.39445565315</v>
+      </c>
+      <c r="C55" s="124">
+        <v>351933.2837347443</v>
+      </c>
+      <c r="D55" s="124">
+        <v>418251.41279293416</v>
+      </c>
+      <c r="E55" s="124">
+        <v>505587.47654576774</v>
+      </c>
+      <c r="F55" s="124">
+        <v>621735.10069409781</v>
+      </c>
+      <c r="H55" s="121"/>
+    </row>
+    <row r="56" spans="1:8" ht="13.15">
+      <c r="A56" s="145">
         <v>30</v>
       </c>
-      <c r="C50" s="124">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D50" s="139">
-        <f>IF($C$17&lt;B50,0,DDM!$C$16)</f>
-        <v>0</v>
-      </c>
-      <c r="E50" s="125">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F50" s="126">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H50" s="121"/>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="B51" s="127" t="s">
-        <v>132</v>
-      </c>
-      <c r="C51" s="124">
-        <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>-1873024.5334744046</v>
-      </c>
-      <c r="D51" s="140">
-        <f>Terminal_Growth</f>
-        <v>0</v>
-      </c>
-      <c r="E51" s="125">
-        <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.46319348808468425</v>
-      </c>
-      <c r="F51" s="126">
-        <f t="shared" si="1"/>
-        <v>-867572.76692819793</v>
-      </c>
-      <c r="H51" s="121"/>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="C52" s="115"/>
-      <c r="E52" s="128" t="s">
-        <v>101</v>
-      </c>
-      <c r="F52" s="138">
-        <f>SUM(F21:F51)</f>
-        <v>-2076884.6114418618</v>
-      </c>
-      <c r="H52" s="121"/>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="C53" s="115"/>
-      <c r="H53" s="121"/>
-    </row>
-    <row r="54" spans="1:8" ht="13.15">
-      <c r="B54" s="120" t="s">
-        <v>130</v>
-      </c>
-      <c r="C54" s="137"/>
-      <c r="D54" s="137"/>
-      <c r="E54" s="118"/>
-      <c r="F54" s="118"/>
-      <c r="H54" s="121"/>
-    </row>
-    <row r="55" spans="1:8" ht="13.15">
-      <c r="A55" s="134">
-        <f>F52</f>
-        <v>-2076884.6114418618</v>
-      </c>
-      <c r="B55" s="132">
-        <f>C78</f>
-        <v>0</v>
-      </c>
-      <c r="C55" s="132">
-        <f>C77</f>
-        <v>0</v>
-      </c>
-      <c r="D55" s="132">
-        <f>C76</f>
+      <c r="B56" s="124">
+        <v>297454.06928013661</v>
+      </c>
+      <c r="C56" s="124">
+        <v>357506.42487900006</v>
+      </c>
+      <c r="D56" s="124">
+        <v>439529.78198205412</v>
+      </c>
+      <c r="E56" s="124">
+        <v>553473.32676061383</v>
+      </c>
+      <c r="F56" s="124">
+        <v>714136.03148038499</v>
+      </c>
+      <c r="H56" s="121"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="C57" s="115"/>
+      <c r="D57" s="115"/>
+      <c r="E57" s="115"/>
+      <c r="F57" s="115"/>
+      <c r="H57" s="121"/>
+    </row>
+    <row r="58" spans="1:8" ht="13.15">
+      <c r="B58" s="120" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="115"/>
+      <c r="D58" s="115"/>
+      <c r="E58" s="115"/>
+      <c r="F58" s="115"/>
+      <c r="H58" s="121"/>
+    </row>
+    <row r="59" spans="1:8" ht="13.15">
+      <c r="B59" s="133">
+        <f>B50</f>
+        <v>0</v>
+      </c>
+      <c r="C59" s="133">
+        <f>C50</f>
         <v>0.02</v>
       </c>
-      <c r="E55" s="132">
-        <f>C75</f>
+      <c r="D59" s="133">
+        <f>D50</f>
         <v>0.04</v>
       </c>
-      <c r="F55" s="132">
-        <f>C74</f>
+      <c r="E59" s="133">
+        <f>E50</f>
         <v>0.06</v>
       </c>
-      <c r="H55" s="121"/>
-    </row>
-    <row r="56" spans="1:8" ht="13.15">
-      <c r="A56" s="144">
+      <c r="F59" s="133">
+        <f>F50</f>
+        <v>0.08</v>
+      </c>
+      <c r="H59" s="121"/>
+    </row>
+    <row r="60" spans="1:8" ht="13.15">
+      <c r="A60" s="144">
+        <v>0</v>
+      </c>
+      <c r="B60" s="125">
+        <f>C7</f>
+        <v>13.25</v>
+      </c>
+      <c r="C60" s="125">
+        <f>C7</f>
+        <v>13.25</v>
+      </c>
+      <c r="D60" s="125">
+        <f>C7</f>
+        <v>13.25</v>
+      </c>
+      <c r="E60" s="142">
+        <f>C7</f>
+        <v>13.25</v>
+      </c>
+      <c r="F60" s="125">
+        <f>C7</f>
+        <v>13.25</v>
+      </c>
+      <c r="H60" s="121"/>
+    </row>
+    <row r="61" spans="1:8" ht="13.15">
+      <c r="A61" s="144">
+        <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
       </c>
-      <c r="B56" s="124">
-        <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>-1789670.8449357809</v>
-      </c>
-      <c r="C56" s="124">
-        <v>-1789670.8449357809</v>
-      </c>
-      <c r="D56" s="124">
-        <v>-1847414.9948403216</v>
-      </c>
-      <c r="E56" s="124">
-        <v>-1906888.5568359671</v>
-      </c>
-      <c r="F56" s="124">
-        <v>-1968167.423112093</v>
-      </c>
-      <c r="H56" s="121"/>
-    </row>
-    <row r="57" spans="1:8" ht="13.15">
-      <c r="A57" s="144">
+      <c r="B61" s="125">
+        <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
+        <v>14.188572306739982</v>
+      </c>
+      <c r="C61" s="125">
+        <f t="shared" si="4"/>
+        <v>14.634858113071347</v>
+      </c>
+      <c r="D61" s="125">
+        <f t="shared" si="4"/>
+        <v>15.093947787930817</v>
+      </c>
+      <c r="E61" s="125">
+        <f t="shared" si="4"/>
+        <v>15.566403206431939</v>
+      </c>
+      <c r="F61" s="125">
+        <f t="shared" si="4"/>
+        <v>16.052803640832188</v>
+      </c>
+      <c r="H61" s="121"/>
+    </row>
+    <row r="62" spans="1:8" ht="13.15">
+      <c r="A62" s="144">
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="B57" s="124">
-        <v>-1789670.8449357804</v>
-      </c>
-      <c r="C57" s="124">
-        <v>-1789670.8449357804</v>
-      </c>
-      <c r="D57" s="124">
-        <v>-1905212.3179819107</v>
-      </c>
-      <c r="E57" s="124">
-        <v>-2032334.1750322436</v>
-      </c>
-      <c r="F57" s="124">
-        <v>-2172422.334293426</v>
-      </c>
-      <c r="H57" s="121"/>
-    </row>
-    <row r="58" spans="1:8" ht="13.15">
-      <c r="A58" s="144">
+      <c r="B62" s="125">
+        <f t="shared" si="4"/>
+        <v>14.594037457807008</v>
+      </c>
+      <c r="C62" s="125">
+        <f t="shared" si="4"/>
+        <v>15.476340600524106</v>
+      </c>
+      <c r="D62" s="125">
+        <f t="shared" si="4"/>
+        <v>16.444380228522771</v>
+      </c>
+      <c r="E62" s="125">
+        <f t="shared" si="4"/>
+        <v>17.508417120364619</v>
+      </c>
+      <c r="F62" s="125">
+        <f t="shared" si="4"/>
+        <v>18.679859268923408</v>
+      </c>
+      <c r="H62" s="121"/>
+    </row>
+    <row r="63" spans="1:8" ht="13.15">
+      <c r="A63" s="144">
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="B58" s="124">
-        <v>-1789670.8449357804</v>
-      </c>
-      <c r="C58" s="124">
-        <v>-1789670.8449357804</v>
-      </c>
-      <c r="D58" s="124">
-        <v>-1976752.5310656261</v>
-      </c>
-      <c r="E58" s="124">
-        <v>-2195868.4467547736</v>
-      </c>
-      <c r="F58" s="124">
-        <v>-2453382.8450112357</v>
-      </c>
-      <c r="H58" s="121"/>
-    </row>
-    <row r="59" spans="1:8" ht="13.15">
-      <c r="A59" s="145">
+      <c r="B63" s="125">
+        <f t="shared" si="4"/>
+        <v>14.694675651837979</v>
+      </c>
+      <c r="C63" s="125">
+        <f t="shared" si="4"/>
+        <v>16.108646397503744</v>
+      </c>
+      <c r="D63" s="125">
+        <f t="shared" si="4"/>
+        <v>17.759785638628777</v>
+      </c>
+      <c r="E63" s="125">
+        <f t="shared" si="4"/>
+        <v>19.695211733650211</v>
+      </c>
+      <c r="F63" s="125">
+        <f t="shared" si="4"/>
+        <v>21.971358502046915</v>
+      </c>
+      <c r="H63" s="121"/>
+    </row>
+    <row r="64" spans="1:8" ht="13.15">
+      <c r="A64" s="145">
+        <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="B59" s="124">
-        <v>-1789670.8449357804</v>
-      </c>
-      <c r="C59" s="124">
-        <v>-1789670.8449357804</v>
-      </c>
-      <c r="D59" s="124">
-        <v>-2049640.5354696955</v>
-      </c>
-      <c r="E59" s="124">
-        <v>-2371884.6442842372</v>
-      </c>
-      <c r="F59" s="124">
-        <v>-2773882.4187256834</v>
-      </c>
-      <c r="H59" s="121"/>
-    </row>
-    <row r="60" spans="1:8" ht="13.15">
-      <c r="A60" s="145">
+      <c r="B64" s="125">
+        <f t="shared" si="4"/>
+        <v>14.631433640772675</v>
+      </c>
+      <c r="C64" s="125">
+        <f t="shared" si="4"/>
+        <v>16.583772887782008</v>
+      </c>
+      <c r="D64" s="125">
+        <f t="shared" si="4"/>
+        <v>18.997166772046651</v>
+      </c>
+      <c r="E64" s="125">
+        <f t="shared" si="4"/>
+        <v>22.00102458019246</v>
+      </c>
+      <c r="F64" s="125">
+        <f t="shared" si="4"/>
+        <v>25.762133179986556</v>
+      </c>
+      <c r="H64" s="121"/>
+    </row>
+    <row r="65" spans="1:8" ht="13.15">
+      <c r="A65" s="145">
+        <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="B60" s="124">
-        <v>-1789670.8449357799</v>
-      </c>
-      <c r="C60" s="124">
-        <v>-1789670.8449357799</v>
-      </c>
-      <c r="D60" s="124">
-        <v>-2117430.4241215452</v>
-      </c>
-      <c r="E60" s="124">
-        <v>-2545266.586795331</v>
-      </c>
-      <c r="F60" s="124">
-        <v>-3109756.227221617</v>
-      </c>
-      <c r="H60" s="121"/>
-    </row>
-    <row r="61" spans="1:8" ht="13.15">
-      <c r="A61" s="145">
+      <c r="B65" s="125">
+        <f t="shared" si="4"/>
+        <v>14.489404273719702</v>
+      </c>
+      <c r="C65" s="125">
+        <f t="shared" si="4"/>
+        <v>16.940791885302616</v>
+      </c>
+      <c r="D65" s="125">
+        <f t="shared" si="4"/>
+        <v>20.133106095186253</v>
+      </c>
+      <c r="E65" s="125">
+        <f t="shared" si="4"/>
+        <v>24.337147453301789</v>
+      </c>
+      <c r="F65" s="125">
+        <f t="shared" si="4"/>
+        <v>29.928072834921089</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
+      <c r="A66" s="145">
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="B61" s="124">
-        <v>-1789670.8449357799</v>
-      </c>
-      <c r="C61" s="124">
-        <v>-1789670.8449357799</v>
-      </c>
-      <c r="D61" s="124">
-        <v>-2177230.5360404709</v>
-      </c>
-      <c r="E61" s="124">
-        <v>-2707640.3125067013</v>
-      </c>
-      <c r="F61" s="124">
-        <v>-3445587.3527309163</v>
-      </c>
-      <c r="H61" s="121"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="C62" s="115"/>
-      <c r="D62" s="115"/>
-      <c r="E62" s="115"/>
-      <c r="F62" s="115"/>
-      <c r="H62" s="121"/>
-    </row>
-    <row r="63" spans="1:8" ht="13.15">
-      <c r="B63" s="120" t="s">
-        <v>131</v>
-      </c>
-      <c r="C63" s="115"/>
-      <c r="D63" s="115"/>
-      <c r="E63" s="115"/>
-      <c r="F63" s="115"/>
-      <c r="H63" s="121"/>
-    </row>
-    <row r="64" spans="1:8" ht="13.15">
-      <c r="B64" s="133">
-        <f>B55</f>
-        <v>0</v>
-      </c>
-      <c r="C64" s="133">
-        <f>C55</f>
-        <v>0</v>
-      </c>
-      <c r="D64" s="133">
-        <f>D55</f>
-        <v>0.02</v>
-      </c>
-      <c r="E64" s="133">
-        <f>E55</f>
-        <v>0.04</v>
-      </c>
-      <c r="F64" s="133">
-        <f>F55</f>
-        <v>0.06</v>
-      </c>
-      <c r="H64" s="121"/>
-    </row>
-    <row r="65" spans="1:8" ht="13.15">
-      <c r="A65" s="144">
-        <v>0</v>
-      </c>
-      <c r="B65" s="125">
-        <f>C12</f>
-        <v>-118.69228650791112</v>
-      </c>
-      <c r="C65" s="125">
-        <f>C12</f>
-        <v>-118.69228650791112</v>
-      </c>
-      <c r="D65" s="125">
-        <f>C12</f>
-        <v>-118.69228650791112</v>
-      </c>
-      <c r="E65" s="142">
-        <f>C12</f>
-        <v>-118.69228650791112</v>
-      </c>
-      <c r="F65" s="125">
-        <f>C12</f>
-        <v>-118.69228650791112</v>
-      </c>
-      <c r="H65" s="121"/>
-    </row>
-    <row r="66" spans="1:8" ht="13.15">
-      <c r="A66" s="144">
-        <f t="shared" ref="A66:A71" si="3">A56</f>
-        <v>5</v>
-      </c>
       <c r="B66" s="125">
-        <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>-118.69228650791111</v>
+        <f t="shared" si="4"/>
+        <v>14.318360086990827</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
+        <v>17.209062687286252</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>-121.47188045749577</v>
+        <v>21.157369615436895</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>-124.33472203290434</v>
+        <v>26.642198609963373</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>-127.28446440888702</v>
-      </c>
-      <c r="H66" s="121"/>
-    </row>
-    <row r="67" spans="1:8" ht="13.15">
-      <c r="A67" s="144">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="B67" s="125">
-        <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
-      </c>
-      <c r="C67" s="125">
-        <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
-      </c>
-      <c r="D67" s="125">
-        <f t="shared" si="4"/>
-        <v>-124.25403397386283</v>
-      </c>
-      <c r="E67" s="125">
-        <f t="shared" si="4"/>
-        <v>-130.37321912597261</v>
-      </c>
-      <c r="F67" s="125">
-        <f t="shared" si="4"/>
-        <v>-137.11655504025211</v>
-      </c>
-      <c r="H67" s="121"/>
+        <v>34.375918522737756</v>
+      </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
-      <c r="A68" s="144">
-        <f t="shared" si="3"/>
-        <v>15</v>
-      </c>
-      <c r="B68" s="125">
-        <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
-      </c>
-      <c r="C68" s="125">
-        <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
-      </c>
-      <c r="D68" s="125">
-        <f t="shared" si="4"/>
-        <v>-127.69772036925049</v>
-      </c>
-      <c r="E68" s="125">
-        <f t="shared" si="4"/>
-        <v>-138.24516585964389</v>
-      </c>
-      <c r="F68" s="125">
-        <f t="shared" si="4"/>
-        <v>-150.64097503698704</v>
-      </c>
-      <c r="H68" s="121"/>
-    </row>
-    <row r="69" spans="1:8" ht="13.15">
-      <c r="A69" s="145">
-        <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="B69" s="125">
-        <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
-      </c>
-      <c r="C69" s="125">
-        <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
-      </c>
-      <c r="D69" s="125">
-        <f t="shared" si="4"/>
-        <v>-131.20628455062251</v>
-      </c>
-      <c r="E69" s="125">
-        <f t="shared" si="4"/>
-        <v>-146.71794723213949</v>
-      </c>
-      <c r="F69" s="125">
-        <f t="shared" si="4"/>
-        <v>-166.06866212587562</v>
-      </c>
-      <c r="H69" s="121"/>
-    </row>
-    <row r="70" spans="1:8" ht="13.15">
-      <c r="A70" s="145">
-        <f t="shared" si="3"/>
-        <v>25</v>
-      </c>
-      <c r="B70" s="125">
-        <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
-      </c>
-      <c r="C70" s="125">
-        <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
-      </c>
-      <c r="D70" s="125">
-        <f t="shared" si="4"/>
-        <v>-134.46944392955865</v>
-      </c>
-      <c r="E70" s="125">
-        <f t="shared" si="4"/>
-        <v>-155.06392512198221</v>
-      </c>
-      <c r="F70" s="125">
-        <f t="shared" si="4"/>
-        <v>-182.2364091177804</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="13.15">
-      <c r="A71" s="145">
-        <f t="shared" si="3"/>
-        <v>30</v>
-      </c>
-      <c r="B71" s="125">
-        <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
-      </c>
-      <c r="C71" s="125">
-        <f t="shared" si="4"/>
-        <v>-118.69228650791111</v>
-      </c>
-      <c r="D71" s="125">
-        <f t="shared" si="4"/>
-        <v>-137.34800443394067</v>
-      </c>
-      <c r="E71" s="125">
-        <f t="shared" si="4"/>
-        <v>-162.88000737975133</v>
-      </c>
-      <c r="F71" s="125">
-        <f t="shared" si="4"/>
-        <v>-198.40210150551155</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="13.15">
-      <c r="B73" s="172" t="s">
+      <c r="B68" s="172" t="s">
         <v>118</v>
       </c>
-      <c r="C73" s="172" t="s">
+      <c r="C68" s="172" t="s">
         <v>133</v>
       </c>
-      <c r="D73" s="172" t="s">
+      <c r="D68" s="172" t="s">
         <v>113</v>
       </c>
-      <c r="E73" s="173" t="s">
+      <c r="E68" s="173" t="s">
         <v>114</v>
       </c>
-      <c r="F73" s="173" t="s">
+      <c r="F68" s="173" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
-      <c r="B74" s="128" t="str">
+    <row r="69" spans="1:8">
+      <c r="B69" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C74" s="143">
+      <c r="C69" s="143">
         <f>Scenarios!C56</f>
-        <v>0.06</v>
-      </c>
-      <c r="D74" s="146">
+        <v>0.08</v>
+      </c>
+      <c r="D69" s="146">
         <f>Scenarios!C55</f>
-        <v>15</v>
-      </c>
-      <c r="E74" s="136">
-        <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>-150.64097503698704</v>
-      </c>
-      <c r="F74" s="143">
+        <v>30</v>
+      </c>
+      <c r="E69" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
+        <v>34.375918522737756</v>
+      </c>
+      <c r="F69" s="143">
         <f>Scenarios!C58</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
-      <c r="B75" s="128" t="str">
+    <row r="70" spans="1:8">
+      <c r="B70" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
       </c>
-      <c r="C75" s="143">
+      <c r="C70" s="143">
         <f>Scenarios!C38</f>
-        <v>0.04</v>
-      </c>
-      <c r="D75" s="146">
+        <v>0.06</v>
+      </c>
+      <c r="D70" s="146">
         <f>Scenarios!C37</f>
-        <v>10</v>
-      </c>
-      <c r="E75" s="136">
-        <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>-130.37321912597261</v>
-      </c>
-      <c r="F75" s="143">
-        <f>Scenarios!C40*(1-F$74-F$78)</f>
+        <v>30</v>
+      </c>
+      <c r="E70" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
+        <v>26.642198609963373</v>
+      </c>
+      <c r="F70" s="143">
+        <f>Scenarios!C40*(1-F$69-F$73)</f>
         <v>0.18</v>
       </c>
-      <c r="H75" s="121"/>
-    </row>
-    <row r="76" spans="1:8">
-      <c r="B76" s="128" t="str">
+      <c r="H70" s="121"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="B71" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
       </c>
-      <c r="C76" s="143">
+      <c r="C71" s="143">
         <f>Scenarios!C26</f>
-        <v>0.02</v>
-      </c>
-      <c r="D76" s="146">
+        <v>0.04</v>
+      </c>
+      <c r="D71" s="146">
         <f>Scenarios!C25</f>
-        <v>10</v>
-      </c>
-      <c r="E76" s="136">
-        <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>-124.25403397386283</v>
-      </c>
-      <c r="F76" s="143">
-        <f>Scenarios!C28*(1-F$74-F$78)</f>
+        <v>30</v>
+      </c>
+      <c r="E71" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
+        <v>21.157369615436895</v>
+      </c>
+      <c r="F71" s="143">
+        <f>Scenarios!C28*(1-F$69-F$73)</f>
         <v>0.53999999999999992</v>
       </c>
-      <c r="H76" s="121"/>
-    </row>
-    <row r="77" spans="1:8">
-      <c r="B77" s="128" t="str">
+      <c r="H71" s="121"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="B72" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C77" s="143">
+      <c r="C72" s="143">
         <f>Scenarios!C32</f>
-        <v>0</v>
-      </c>
-      <c r="D77" s="146">
+        <v>0.02</v>
+      </c>
+      <c r="D72" s="146">
         <f>Scenarios!C31</f>
-        <v>10</v>
-      </c>
-      <c r="E77" s="136">
-        <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>-118.69228650791111</v>
-      </c>
-      <c r="F77" s="143">
-        <f>Scenarios!C34*(1-F$74-F$78)</f>
+        <v>30</v>
+      </c>
+      <c r="E72" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
+        <v>17.209062687286252</v>
+      </c>
+      <c r="F72" s="143">
+        <f>Scenarios!C34*(1-F$69-F$73)</f>
         <v>0.18</v>
       </c>
-      <c r="H77" s="121"/>
-    </row>
-    <row r="78" spans="1:8">
-      <c r="B78" s="128" t="str">
+      <c r="H72" s="121"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="B73" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C78" s="143">
+      <c r="C73" s="143">
         <f>Scenarios!C50</f>
         <v>0</v>
       </c>
-      <c r="D78" s="146">
+      <c r="D73" s="146">
         <f>Scenarios!C49</f>
-        <v>15</v>
-      </c>
-      <c r="E78" s="136">
-        <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>-118.69228650791111</v>
-      </c>
-      <c r="F78" s="143">
+        <v>30</v>
+      </c>
+      <c r="E73" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
+        <v>14.318360086990827</v>
+      </c>
+      <c r="F73" s="143">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
-      <c r="B79" s="156"/>
-      <c r="C79" s="156"/>
-      <c r="D79" s="156"/>
-      <c r="E79" s="156"/>
-      <c r="F79" s="157"/>
-    </row>
-    <row r="80" spans="1:8">
-      <c r="B80" s="156" t="s">
-        <v>314</v>
-      </c>
-      <c r="C80" s="156" t="s">
+    <row r="74" spans="1:8">
+      <c r="B74" s="156"/>
+      <c r="C74" s="156"/>
+      <c r="D74" s="156"/>
+      <c r="E74" s="156"/>
+      <c r="F74" s="157"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="B75" s="156" t="s">
+        <v>313</v>
+      </c>
+      <c r="C75" s="156" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="81" spans="3:3">
-      <c r="C81" s="156" t="s">
+    <row r="76" spans="1:8">
+      <c r="C76" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="82" spans="3:3">
-      <c r="C82" s="156" t="s">
+    <row r="77" spans="1:8">
+      <c r="C77" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="92" spans="3:3">
-      <c r="C92" s="116"/>
-    </row>
-    <row r="93" spans="3:3">
-      <c r="C93" s="116"/>
-    </row>
-    <row r="94" spans="3:3">
-      <c r="C94" s="116"/>
+    <row r="87" spans="3:3">
+      <c r="C87" s="116"/>
+    </row>
+    <row r="88" spans="3:3">
+      <c r="C88" s="116"/>
+    </row>
+    <row r="89" spans="3:3">
+      <c r="C89" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="E6:F9"/>
+    <mergeCell ref="E6:F6"/>
   </mergeCells>
-  <conditionalFormatting sqref="C21:F50">
+  <conditionalFormatting sqref="C16:F45">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E65 B66:F71">
+  <conditionalFormatting sqref="E60 B61:F66">
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>ISNUMBER(MATCH(B65, $E$75:$E$78, 0))</formula>
+      <formula>ISNUMBER(MATCH(B60, $E$70:$E$73, 0))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C17" xr:uid="{0679E683-700B-4E49-B936-C44C7B75B2A2}">
-      <formula1>$A$56:$A$61</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12" xr:uid="{0679E683-700B-4E49-B936-C44C7B75B2A2}">
+      <formula1>$A$51:$A$56</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18385,7 +18338,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="275" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I2" s="276"/>
     </row>
@@ -18439,7 +18392,7 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="274">
@@ -18447,7 +18400,7 @@
       </c>
       <c r="I6" s="262">
         <f t="shared" si="0"/>
-        <v>-124.33563243722989</v>
+        <v>22.812920556327281</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18462,11 +18415,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="359" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
-        <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 兴业银行(601166.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
-      </c>
-      <c r="F7" s="358"/>
+        <v>Please develop three logical 30-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 30-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 兴业银行(601166.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
+      </c>
+      <c r="F7" s="359"/>
       <c r="H7" s="274">
         <v>4</v>
       </c>
@@ -18481,14 +18434,14 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>-206364</v>
+        <v>137471</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
+      <c r="E8" s="359"/>
+      <c r="F8" s="359"/>
       <c r="H8" s="274">
         <v>5</v>
       </c>
@@ -18503,14 +18456,14 @@
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
-        <v>-143173.66759486249</v>
+        <v>114702.58240513749</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
+      <c r="E9" s="359"/>
+      <c r="F9" s="359"/>
       <c r="H9" s="274">
         <v>6</v>
       </c>
@@ -18520,8 +18473,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
+      <c r="E10" s="359"/>
+      <c r="F10" s="359"/>
       <c r="H10" s="274">
         <v>7</v>
       </c>
@@ -18532,10 +18485,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>278</v>
-      </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
+        <v>457</v>
+      </c>
+      <c r="E11" s="359"/>
+      <c r="F11" s="359"/>
       <c r="H11" s="274">
         <v>8</v>
       </c>
@@ -18553,8 +18506,8 @@
         <v>-5.5054441259114184E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
+      <c r="E12" s="359"/>
+      <c r="F12" s="359"/>
       <c r="H12" s="274">
         <v>9</v>
       </c>
@@ -18571,8 +18524,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-1.3520092995664894</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
+      <c r="E13" s="359"/>
+      <c r="F13" s="359"/>
       <c r="H13" s="274">
         <v>10</v>
       </c>
@@ -18587,10 +18540,10 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>7.6158467823697729E-2</v>
-      </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+        <v>-2.7745066708446342E-2</v>
+      </c>
+      <c r="E14" s="359"/>
+      <c r="F14" s="359"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -18606,7 +18559,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -18614,27 +18567,27 @@
         <v>134</v>
       </c>
       <c r="C18" s="151">
-        <v>10</v>
-      </c>
-      <c r="E18" s="358" t="s">
-        <v>335</v>
-      </c>
-      <c r="F18" s="359"/>
+        <v>30</v>
+      </c>
+      <c r="E18" s="359" t="s">
+        <v>334</v>
+      </c>
+      <c r="F18" s="360"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="360"/>
+      <c r="F19" s="360"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>307</v>
-      </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+        <v>306</v>
+      </c>
+      <c r="E20" s="360"/>
+      <c r="F20" s="360"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -18644,23 +18597,23 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="360"/>
+      <c r="F21" s="360"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C22" s="161">
-        <f>DCF!C12</f>
-        <v>-118.69228650791112</v>
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
+        <v>13.25</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="360"/>
+      <c r="F22" s="360"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -18677,37 +18630,37 @@
       </c>
       <c r="C25" s="167">
         <f>C18</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="358"/>
+      <c r="F25" s="358"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
         <v>135</v>
       </c>
       <c r="C26" s="165">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="358"/>
+      <c r="F26" s="358"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>DCF!E76</f>
-        <v>-124.25403397386283</v>
+        <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
+        <v>21.157369615436895</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="358"/>
+      <c r="F27" s="358"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -18717,8 +18670,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="358"/>
+      <c r="F28" s="358"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -18735,37 +18688,37 @@
       </c>
       <c r="C31" s="167">
         <f>C18</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="358"/>
+      <c r="F31" s="358"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
         <v>135</v>
       </c>
       <c r="C32" s="165">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="358"/>
+      <c r="F32" s="358"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>DCF!E77</f>
-        <v>-118.69228650791111</v>
+        <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
+        <v>17.209062687286252</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="358"/>
+      <c r="F33" s="358"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -18775,8 +18728,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="358"/>
+      <c r="F34" s="358"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -18793,37 +18746,37 @@
       </c>
       <c r="C37" s="167">
         <f>C18</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
         <v>135</v>
       </c>
       <c r="C38" s="165">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="358"/>
+      <c r="F38" s="358"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>DCF!E75</f>
-        <v>-130.37321912597261</v>
+        <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
+        <v>26.642198609963373</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="358"/>
+      <c r="F39" s="358"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -18834,8 +18787,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="358"/>
+      <c r="F40" s="358"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -18843,7 +18796,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>-124.36552151109444</v>
+        <v>21.464674028712061</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -18869,7 +18822,7 @@
         <v>134</v>
       </c>
       <c r="C46" s="151">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
@@ -18894,11 +18847,11 @@
       </c>
       <c r="C49" s="167">
         <f>C46</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="358"/>
+      <c r="F49" s="358"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -18908,23 +18861,23 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="358"/>
+      <c r="F50" s="358"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>DCF!E78</f>
-        <v>-118.69228650791111</v>
+        <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
+        <v>14.318360086990827</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="358"/>
+      <c r="F51" s="358"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -18934,12 +18887,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="358"/>
+      <c r="F52" s="358"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -18952,37 +18905,37 @@
       </c>
       <c r="C55" s="167">
         <f>C46</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="358"/>
+      <c r="F55" s="358"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
         <v>135</v>
       </c>
       <c r="C56" s="165">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="358"/>
+      <c r="F56" s="358"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>DCF!E74</f>
-        <v>-150.64097503698704</v>
+        <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
+        <v>34.375918522737756</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="358"/>
+      <c r="F57" s="358"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -18992,8 +18945,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="358"/>
+      <c r="F58" s="358"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19001,14 +18954,14 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>-125.39563243722989</v>
+        <v>21.752920556327282</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F60" s="307">
         <f>Thesis!F28</f>
@@ -19017,7 +18970,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19026,10 +18979,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E63" s="279" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -19038,11 +18991,11 @@
       </c>
       <c r="C64" s="167">
         <f>C18</f>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="278" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -19050,11 +19003,11 @@
         <v>135</v>
       </c>
       <c r="C65" s="152">
-        <v>4.6574870890079501E-2</v>
+        <v>4.2510316586672814E-2</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="278" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -19062,50 +19015,50 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>DCF!C18</f>
-        <v>-132.51771555894882</v>
+        <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
+        <v>21.74944849239106</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E66" s="278" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E68" s="279" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C69" s="271" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
-        <v>Y</v>
+        <v>N</v>
       </c>
       <c r="E69" s="135"/>
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C70" s="271" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="E70" s="278" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C71" s="271" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19115,18 +19068,18 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C72" s="270" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F72" s="324">
         <f>BS!D89/C60</f>
-        <v>0.25953075229842365</v>
+        <v>-16.310580250078065</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19145,7 +19098,7 @@
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="273" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C76" s="272">
         <f>F60</f>
@@ -19168,12 +19121,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
@@ -19198,7 +19151,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>-45.698116777416153</v>
+        <v>7.9274491823350175</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -19208,7 +19161,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>-44.013860217649388</v>
+        <v>9.6117057421017815</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19219,7 +19172,7 @@
       </c>
       <c r="F83" s="324">
         <f>(1-C83/C60)</f>
-        <v>0.64900005397172267</v>
+        <v>0.55814182664745582</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19227,12 +19180,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C86" s="264">
         <f>Market_Price</f>
@@ -19245,11 +19198,11 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>302</v>
-      </c>
-      <c r="C87" s="263" t="e">
+        <v>301</v>
+      </c>
+      <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>#NUM!</v>
+        <v>3.3241061492891966E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19257,12 +19210,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
@@ -19287,7 +19240,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>-69.056238428122782</v>
+        <v>11.97948317057776</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -19297,7 +19250,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>-66.891462521769384</v>
+        <v>14.144259076931155</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19308,19 +19261,19 @@
       </c>
       <c r="F93" s="324">
         <f>(1-C93/C60)</f>
-        <v>0.46655667967340342</v>
+        <v>0.34977654884061038</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="311"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
@@ -19347,7 +19300,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>-99.543095911787674</v>
+        <v>17.268169673963001</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -19355,21 +19308,21 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>-96.811373105304924</v>
+        <v>19.999892480445755</v>
       </c>
       <c r="D99" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
       <c r="F99" s="324">
         <f>(1-C99/C60)</f>
-        <v>0.22795259114174948</v>
+        <v>8.0588170739750331E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19377,12 +19330,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C102" s="135">
         <f>Thesis!F32</f>
@@ -19405,27 +19358,27 @@
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>-89.254134330890878</v>
+        <v>15.483299184248073</v>
       </c>
       <c r="D104" s="117"/>
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>-86.708193186576011</v>
+        <v>18.029240328562945</v>
       </c>
       <c r="D105" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
       <c r="F105" s="324">
         <f>(1-C105/C66)</f>
-        <v>0.34568602529218084</v>
+        <v>0.17104839072722289</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -19433,32 +19386,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="315" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F107" s="312"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="308" t="s">
+        <v>329</v>
+      </c>
+      <c r="F108" s="313" t="s">
         <v>330</v>
-      </c>
-      <c r="F108" s="313" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="309" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F109" s="313" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="310" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F110" s="314" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
